--- a/AAII_Financials/Quarterly/ORCL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ORCL_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,386 +656,410 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="31" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="19" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45351</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45260</v>
+      </c>
+      <c r="F7" s="2">
         <v>45169</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45077</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44985</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44895</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44804</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44712</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44620</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44530</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44439</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44347</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44255</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44165</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44074</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43982</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43890</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43799</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43708</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43616</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43524</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43434</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43343</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43251</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43159</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43069</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42978</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42886</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42794</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42704</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>13280000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>12941000</v>
+      </c>
+      <c r="F8" s="3">
         <v>12453000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>13836000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>12398000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>12275000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>11445000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>11840000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>10513000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>10360000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>9728000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>11227000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>10085000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>9800000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>9367000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>10439000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>9796000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>9614000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>9218000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>11137000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>9614000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>9562000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>9193000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>11014000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>9676000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>9589000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>9104000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>10893000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>9205000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>9035000</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3869000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3740000</v>
+      </c>
+      <c r="F9" s="3">
         <v>3610000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>3730000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>3439000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>3358000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>3037000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>2397000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>2218000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>2159000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>2103000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>2122000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>1915000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1939000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1880000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1969000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1964000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>2048000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1957000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>2063000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1976000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>2001000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1953000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>2173000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>2881000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>2843000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>2777000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>2442000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>1885000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>1790000</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>9411000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>9201000</v>
+      </c>
+      <c r="F10" s="3">
         <v>8843000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>10106000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>8959000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>8917000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>8408000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>9443000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>8295000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>8201000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>7625000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>9105000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>8170000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>7861000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>7487000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>8470000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>7832000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>7566000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>7261000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>9074000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>7638000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>7561000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>7240000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>8841000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>6795000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>6746000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>6327000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>8451000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>7320000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>7245000</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1067,97 +1091,105 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>2216000</v>
+        <v>2248000</v>
       </c>
       <c r="E12" s="3">
         <v>2226000</v>
       </c>
       <c r="F12" s="3">
+        <v>2216000</v>
+      </c>
+      <c r="G12" s="3">
+        <v>2226000</v>
+      </c>
+      <c r="H12" s="3">
         <v>2146000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>2158000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>2093000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>1965000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>1816000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>1754000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>1684000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1715000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1928000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>1601000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>1589000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>1479000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>1500000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>1531000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>1557000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>1562000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>1426000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>1475000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>1564000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>1543000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>1496000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>1473000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>1572000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>1608000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>1521000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>1510000</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1245,186 +1277,204 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>245000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>130000</v>
+      </c>
+      <c r="F14" s="3">
         <v>149000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>181000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>115000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>199000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>185000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>108000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>39000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>4699000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>59000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>125000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>79000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>172000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>193000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>81000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>67000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>54000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>103000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>183000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>39000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>161000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>104000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>102000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>94000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>309000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>136000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>136000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>191000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>749000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>755000</v>
+      </c>
+      <c r="F15" s="3">
         <v>763000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>870000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>886000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>907000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>919000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>268000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>279000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>299000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>303000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>342000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>347000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>345000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>345000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>365000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>400000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>407000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>414000</v>
-      </c>
-      <c r="U15" s="3">
-        <v>424000</v>
-      </c>
-      <c r="V15" s="3">
-        <v>407000</v>
       </c>
       <c r="W15" s="3">
         <v>424000</v>
       </c>
       <c r="X15" s="3">
+        <v>407000</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>424000</v>
+      </c>
+      <c r="Z15" s="3">
         <v>434000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>415000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>394000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>400000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>411000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>441000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>397000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>302000</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1453,186 +1503,200 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>9530000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>9319000</v>
+      </c>
+      <c r="F17" s="3">
         <v>9157000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>9696000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>9138000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>9204000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>8822000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>7338000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>6691000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>11184000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>6301000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>6686000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>6207000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>6217000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>6156000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>6131000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>6268000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>6431000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>6341000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>6880000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>6215000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>6461000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>6415000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>6853000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>6361000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>6550000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>6355000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>6819000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>6246000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>5998000</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>3750000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>3622000</v>
+      </c>
+      <c r="F18" s="3">
         <v>3296000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>4140000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>3260000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>3071000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>2623000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>4502000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>3822000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-824000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>3427000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>4541000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>3878000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>3583000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>3211000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>4308000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>3528000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>3183000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>2877000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>4257000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>3399000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>3101000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>2778000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>4161000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>3315000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>3039000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>2749000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>4074000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>2959000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>3037000</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1664,453 +1728,485 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-49000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-76000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-134000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-71000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-180000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-174000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-315000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>7000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-41000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>312000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-17000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-11000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-33000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>4000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>92000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>99000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>134000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>198000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>192000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>291000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>294000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>409000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>262000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>220000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>168000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>189000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>99000</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>5298000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>5161000</v>
+      </c>
+      <c r="F21" s="3">
         <v>4722000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>5650000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>4684000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>4498000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>3909000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>5159000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>4282000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-58000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>4143000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>5605000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>4593000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>4303000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>3910000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>4997000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>4280000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>4023000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>3726000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>5145000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>4338000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>3997000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>3789000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>5157000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>4423000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>3989000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>3665000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>4961000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>3804000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>3679000</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>876000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>888000</v>
+      </c>
+      <c r="F22" s="3">
         <v>872000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>955000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>908000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>856000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>787000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>704000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>667000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>679000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>705000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>697000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>585000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>600000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>614000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>579000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>456000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>465000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>494000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>525000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>509000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>519000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>529000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>548000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>533000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>475000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>469000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>481000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>450000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>451000</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>2865000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2720000</v>
+      </c>
+      <c r="F23" s="3">
         <v>2375000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>3109000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>2218000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>2144000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>1656000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>3624000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>2840000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-1496000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>2681000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>4156000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>3276000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>2972000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>2595000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>3696000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>3076000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>2810000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>2482000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>3866000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>3088000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>2774000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>2540000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>3907000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>3191000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>2826000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>2500000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>3761000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>2698000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>2685000</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>464000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>217000</v>
+      </c>
+      <c r="F24" s="3">
         <v>-45000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-210000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>322000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>403000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>108000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>435000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>521000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-249000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>224000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>124000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-1745000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>530000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>344000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>580000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>505000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>499000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>345000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>126000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>579000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>441000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>428000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>632000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>367000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>612000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>356000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>529000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>459000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>653000</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2198,186 +2294,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>2401000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2503000</v>
+      </c>
+      <c r="F26" s="3">
         <v>2420000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>3319000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>1896000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>1741000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1548000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>3189000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>2319000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1247000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>2457000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>4032000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>5021000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>2442000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>2251000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>3116000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>2571000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>2311000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>2137000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>3740000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>2509000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>2333000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>2112000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>3275000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>2824000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>2214000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>2144000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>3232000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>2239000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>2032000</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>2401000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2503000</v>
+      </c>
+      <c r="F27" s="3">
         <v>2420000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>3319000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>1896000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>1741000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1548000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>3189000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>2319000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-1247000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>2457000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>4032000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>5021000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>2442000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>2251000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>3116000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>2571000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>2311000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>2137000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>3740000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>2509000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>2333000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>2112000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>3275000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>2824000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>2214000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>2144000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>3232000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>2239000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>2032000</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2465,8 +2579,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2506,15 +2626,15 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
@@ -2525,37 +2645,43 @@
         <v>0</v>
       </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>236000</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>153000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="AA29" s="3">
         <v>1000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AB29" s="3">
         <v>-6871000</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB29" s="3">
-        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>24</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2643,8 +2769,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2732,186 +2864,204 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>14000</v>
+      </c>
+      <c r="F32" s="3">
         <v>49000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>76000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>134000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>71000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>180000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>174000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>315000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-7000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>41000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-312000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>17000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>11000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>2000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>33000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-4000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-92000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-99000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-134000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-198000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-192000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-291000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-294000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-409000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-262000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-220000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-168000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-189000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-99000</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2401000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>2503000</v>
+      </c>
+      <c r="F33" s="3">
         <v>2420000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>3319000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>1896000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>1741000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1548000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>3189000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>2319000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-1247000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>2457000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>4032000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>5021000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>2442000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>2251000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>3116000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>2571000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>2311000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>2137000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>3740000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>2745000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>2333000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>2265000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>3276000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-4047000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>2214000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>2144000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>3232000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>2239000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>2032000</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2999,191 +3149,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2401000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>2503000</v>
+      </c>
+      <c r="F35" s="3">
         <v>2420000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>3319000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>1896000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>1741000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1548000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>3189000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>2319000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-1247000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>2457000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>4032000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>5021000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>2442000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>2251000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>3116000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>2571000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>2311000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>2137000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>3740000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>2745000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>2333000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>2265000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>3276000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-4047000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>2214000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>2144000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>3232000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>2239000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>2032000</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45351</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45260</v>
+      </c>
+      <c r="F38" s="2">
         <v>45169</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45077</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44985</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44895</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44804</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44712</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44620</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44530</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44439</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44347</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44255</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44165</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44074</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43982</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43890</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43799</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43708</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43616</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43524</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43434</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43343</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43251</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43159</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43069</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42978</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42886</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42794</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42704</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3215,8 +3383,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3248,275 +3418,295 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9481000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>8244000</v>
+      </c>
+      <c r="F41" s="3">
         <v>11613000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>9765000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>8219000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>6813000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>10448000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>21383000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>22682000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>17938000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>23059000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>30098000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>22321000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>28001000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>27276000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>37239000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>23829000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>24540000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>31083000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>20514000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>14720000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>10824000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>18455000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>21620000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>19487000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>21310000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>21321000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>21784000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>19748000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>18592000</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>423000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>446000</v>
+      </c>
+      <c r="F42" s="3">
         <v>470000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>422000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>550000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>537000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>772000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>519000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>707000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>4900000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>16251000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>16456000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>13543000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>10592000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>15003000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>5818000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>2029000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>2904000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>4621000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>17313000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>25310000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>38567000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>41639000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>45641000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>50968000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>50270000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>45576000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>44294000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>39604000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>39614000</v>
       </c>
     </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7297000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>6804000</v>
+      </c>
+      <c r="F43" s="3">
         <v>6519000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>6915000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>6213000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>6197000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>5937000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>5953000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>4588000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>4462000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>4482000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>5409000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>4637000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>4423000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>4576000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>6329000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>4162000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>4050000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>3820000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>5910000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>3993000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>3975000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>3729000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>5938000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>3902000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>3798000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>3591000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>5300000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>3721000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>3690000</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3550,240 +3740,258 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>24</v>
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3">
+        <v>0</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q44" s="3">
-        <v>211000</v>
+      <c r="Q44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="R44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>24</v>
+      <c r="S44" s="3">
+        <v>211000</v>
       </c>
       <c r="T44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="U44" s="3">
-        <v>320000</v>
+      <c r="U44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="V44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>24</v>
+      <c r="W44" s="3">
+        <v>320000</v>
       </c>
       <c r="X44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Y44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA44" s="3">
         <v>398000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>496000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>436000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>312000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>300000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>391000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3862000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>3795000</v>
+      </c>
+      <c r="F45" s="3">
         <v>3564000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>3902000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>3714000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>4014000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>3847000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>3778000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>3698000</v>
       </c>
       <c r="K45" s="3">
         <v>3778000</v>
       </c>
       <c r="L45" s="3">
+        <v>3698000</v>
+      </c>
+      <c r="M45" s="3">
+        <v>3778000</v>
+      </c>
+      <c r="N45" s="3">
         <v>3325000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>3604000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>3243000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>3235000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>3084000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>2543000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>3422000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>3046000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>2860000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>2329000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>3594000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>3572000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>3186000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>5986000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>2879000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>2731000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>2535000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>2837000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>2547000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>2511000</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>21063000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>19289000</v>
+      </c>
+      <c r="F46" s="3">
         <v>22166000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>21004000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>18696000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>17561000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>21004000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>31633000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>31675000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>31078000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>47117000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>55567000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>43744000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>46251000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>49939000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>52140000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>33442000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>34540000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>42384000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>46386000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>47617000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>56938000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>67009000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>76159000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>77732000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>78545000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>73335000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>74515000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>66011000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>64734000</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3871,186 +4079,204 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>19117000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>18009000</v>
+      </c>
+      <c r="F48" s="3">
         <v>17644000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>17069000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>16345000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>14351000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>12280000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>9716000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>8609000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>8029000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>7610000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>7049000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>6816000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>6627000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>6401000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>9044000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>8048000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>8170000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>8264000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>6252000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>6197000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>6003000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>5918000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>5897000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>5904000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>5868000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>5586000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>5315000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>5070000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>4882000</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>69851000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>70609000</v>
+      </c>
+      <c r="F49" s="3">
         <v>71280000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>72098000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>72206000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>73106000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>74128000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>45251000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>45521000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>45723000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>46043000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>46365000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>46708000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>46938000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>47272000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>47507000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>47869000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>48302000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>48594000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>49058000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>49454000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>49881000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>49997000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>50425000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>49365000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>49758000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>50206000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>50724000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>50292000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>50051000</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4138,8 +4364,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4227,97 +4459,109 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>27051000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>26417000</v>
+      </c>
+      <c r="F52" s="3">
         <v>25572000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>24213000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>24373000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>23451000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>22897000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>22697000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>22839000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>22067000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>22154000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>22126000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>20841000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>10198000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>9934000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>6747000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>7345000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>7431000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>6987000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>7013000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>6170000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>5496000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>5434000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>5370000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>5200000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>4591000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>4470000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>4437000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>4009000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>3933000</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4405,97 +4649,109 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>137082000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>134324000</v>
+      </c>
+      <c r="F54" s="3">
         <v>136662000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>134384000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>131620000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>128469000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>130309000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>109297000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>108644000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>106897000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>122924000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>131107000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>118109000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>110014000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>113546000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>115438000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>96704000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>98443000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>106229000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>108709000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>109438000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>118318000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>128358000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>137851000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>138201000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>138762000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>133597000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>134991000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>125382000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>123600000</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4527,8 +4783,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4560,542 +4818,580 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1658000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1107000</v>
+      </c>
+      <c r="F57" s="3">
         <v>1034000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1204000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1610000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1647000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1461000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1317000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1124000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1034000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>749000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>745000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>812000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>724000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>534000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>637000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>533000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>534000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>486000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>580000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>603000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>587000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>527000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>529000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>603000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>554000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>593000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>599000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>481000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>615000</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5510000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>6321000</v>
+      </c>
+      <c r="F58" s="3">
         <v>4499000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>4061000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>5415000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>9746000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>16097000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>3749000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>6248000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>4998000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>6748000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>8250000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>5758000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>7251000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>2997000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>2371000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>2355000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>999000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>3748000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>4494000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>4487000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>6477000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>3743000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>4491000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>4491000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>2499000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>4998000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>9797000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>3498000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>3838000</v>
       </c>
     </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>17717000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>16979000</v>
+      </c>
+      <c r="F59" s="3">
         <v>19824000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>17825000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>15855000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>15713000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>17261000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>14445000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>13461000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>12849000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>15574000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>15169000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>13680000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>13372000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>15217000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>14192000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>12852000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>13059000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>14641000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>13556000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>12896000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>13251000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>15292000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>14104000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>12874000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>12441000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>14635000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>13782000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>11811000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>11894000</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>24885000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>24407000</v>
+      </c>
+      <c r="F60" s="3">
         <v>25357000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>23090000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>22880000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>27106000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>34819000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>19511000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>20833000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>18881000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>23071000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>24164000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>20250000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>21347000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>18748000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>17200000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>15740000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>14592000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>18875000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>18630000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>17986000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>20315000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>19562000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>19124000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>17968000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>15494000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>20226000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>24178000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>15790000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>16347000</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>82470000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>82468000</v>
+      </c>
+      <c r="F61" s="3">
         <v>84442000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>86420000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>86396000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>81173000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>75480000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>72110000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>72165000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>73433000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>75970000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>75995000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>63541000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>63531000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>67769000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>69209000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>49299000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>50643000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>50684000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>51656000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>51672000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>51561000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>54386000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>56128000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>55145000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>57119000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>47355000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>47132000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>49518000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>51427000</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>23545000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>23071000</v>
+      </c>
+      <c r="F62" s="3">
         <v>24022000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>23318000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>24256000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>23966000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>25459000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>23444000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>23857000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>24241000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>25013000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>24996000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>24681000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>16520000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>16889000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>16312000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>16784000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>17023000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>17651000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>16060000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>15542000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>15387000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>15846000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>15726000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>16816000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>9849000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>9650000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>9435000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>9051000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>6981000</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5183,8 +5479,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5272,8 +5574,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5361,97 +5669,109 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>131459000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>130458000</v>
+      </c>
+      <c r="F66" s="3">
         <v>134292000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>133311000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>134041000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>132715000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>136184000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>115517000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>117340000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>116998000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>124465000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>125869000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>109209000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>102097000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>104055000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>103364000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>82469000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>82880000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>87796000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>86924000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>85724000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>87746000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>90291000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>91479000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>90412000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>82894000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>77638000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>81131000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>74767000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>75138000</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5483,8 +5803,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5572,8 +5894,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5661,8 +5989,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5750,8 +6084,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5839,97 +6179,109 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-24533000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-25431000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-26428000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-27620000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-29721000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-30617000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-31134000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-31336000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-33147000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-34076000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-25679000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-20120000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-16206000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-17095000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-15410000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-12696000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-10771000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-9174000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-6446000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-3496000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-1284000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>5107000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>12022000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>19111000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>20037000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>28296000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>28586000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>27598000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>25576000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>24375000</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6017,8 +6369,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6106,8 +6464,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6195,97 +6559,109 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5623000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3866000</v>
+      </c>
+      <c r="F76" s="3">
         <v>2370000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1073000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-2421000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-4246000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-5875000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-6220000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-8696000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-10101000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-1541000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>5238000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>8900000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>7917000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>9491000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>12074000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>14235000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>15563000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>18433000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>21785000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>23714000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>30572000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>38067000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>46372000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>47789000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>55868000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>55959000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>53860000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>50615000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>48462000</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6373,191 +6749,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45351</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45260</v>
+      </c>
+      <c r="F80" s="2">
         <v>45169</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45077</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44985</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44895</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44804</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44712</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44620</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44530</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44439</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44347</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44255</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44165</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44074</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43982</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43890</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43799</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43708</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43616</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43524</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43434</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43343</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43251</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43159</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43069</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42978</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42886</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42794</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42704</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2401000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>2503000</v>
+      </c>
+      <c r="F81" s="3">
         <v>2420000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>3319000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>1896000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>1741000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1548000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>3189000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>2319000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-1247000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>2457000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>4032000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>5021000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>2442000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>2251000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>3116000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>2571000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>2311000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>2137000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>3740000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>2745000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>2333000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>2265000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>3276000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-4047000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>2214000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>2144000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>3232000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>2239000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>2032000</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6589,97 +6983,105 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1557000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1553000</v>
+      </c>
+      <c r="F83" s="3">
         <v>1475000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1586000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>1558000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>1498000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1466000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>831000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>775000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>759000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>757000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>752000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>732000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>731000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>701000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>722000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>748000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>748000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>750000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>754000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>741000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>704000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>720000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>702000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>699000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>688000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>696000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>719000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>656000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>543000</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6767,8 +7169,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6856,8 +7264,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6945,8 +7359,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7034,8 +7454,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7123,97 +7549,109 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5475000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>143000</v>
+      </c>
+      <c r="F89" s="3">
         <v>6974000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>5647000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>4275000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>849000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>6394000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>3985000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>3845000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-3682000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>5391000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>4842000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>3704000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1388000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>5953000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>3614000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>3012000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>513000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>6000000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>4422000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>2861000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>546000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>6722000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>4660000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>3310000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>850000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>6566000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>4466000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>2699000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>1086000</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7245,97 +7683,105 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1674000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1080000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1314000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1913000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-2628000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-2435000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1719000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1423000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1101000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-925000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1062000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-717000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-414000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-568000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-436000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-433000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-396000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-349000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-386000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-413000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-443000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-421000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-383000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-378000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-286000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-599000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-473000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-525000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-440000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-757000</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7423,8 +7869,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7512,97 +7964,109 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1783000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1249000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1562000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1612000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-2778000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-2658000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-29436000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1161000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>2432000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>10730000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-781000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-3911000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-3384000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>3852000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-9655000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-4256000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>480000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>1233000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>12386000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>7906000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>13199000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>1920000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>3532000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>3160000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-1257000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-5710000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-1818000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-5846000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-728000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-9717000</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7634,97 +8098,105 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-1099000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>-1099000</v>
+      </c>
+      <c r="F96" s="3">
         <v>-1091000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>-1082000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>-863000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>-863000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>-860000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>-854000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>-855000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-861000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-887000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-917000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-699000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-717000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-730000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-740000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-768000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-767000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-795000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-806000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-670000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-714000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-742000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-778000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-783000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-791000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-788000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-787000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-612000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-614000</v>
       </c>
     </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7812,8 +8284,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7901,8 +8379,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7990,271 +8474,295 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2463000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-2289000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-3528000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-2440000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-105000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-1855000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>12310000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-4026000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-1579000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-12053000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-11468000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>6798000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-6129000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-4554000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-6493000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>14133000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-4169000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-8294000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-7802000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-6461000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-12239000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-10023000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-13333000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-5459000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-4020000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>4938000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-5441000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>3287000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-940000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-973000</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>26000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-36000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-49000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>14000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>29000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-203000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-97000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>46000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-116000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-181000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>48000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>129000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>39000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>232000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-81000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-34000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>5000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-15000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-73000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>75000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-74000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-86000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-228000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>144000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-89000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>230000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>129000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>125000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-418000</v>
       </c>
     </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1237000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-3369000</v>
+      </c>
+      <c r="F102" s="3">
         <v>1848000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1546000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>1406000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-3635000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-10935000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-1299000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>4744000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-5121000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-7039000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>7777000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-5680000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>725000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-9963000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>13410000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-711000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-6543000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>10569000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>5794000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>3896000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-7631000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-3165000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>2133000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-1823000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-463000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>2036000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>1156000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-10022000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ORCL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ORCL_QTR_FIN.xlsx
@@ -656,410 +656,434 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="19" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="21" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45535</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45443</v>
+      </c>
+      <c r="F7" s="2">
         <v>45351</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45260</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45169</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45077</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44985</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44895</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44804</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44712</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44620</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44530</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44439</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44347</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44255</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44165</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44074</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43982</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43890</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43799</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43708</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43616</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43524</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43434</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43343</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43251</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43159</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43069</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42978</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42886</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42794</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42704</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>13307000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>14287000</v>
+      </c>
+      <c r="F8" s="3">
         <v>13280000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>12941000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>12453000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>13836000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>12398000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>12275000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>11445000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>11840000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>10513000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>10360000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>9728000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>11227000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>10085000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>9800000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>9367000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>10439000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>9796000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>9614000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>9218000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>11137000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>9614000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>9562000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>9193000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>11014000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>9676000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>9589000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>9104000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>10893000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>9205000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>9035000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3906000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3924000</v>
+      </c>
+      <c r="F9" s="3">
         <v>3869000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>3740000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>3610000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>3730000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>3439000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>3358000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>3037000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>2397000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>2218000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>2159000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>2103000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>2122000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1915000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1939000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1880000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>1969000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1964000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>2048000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1957000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>2063000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1976000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>2001000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>1953000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>2173000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>2881000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>2843000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>2777000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>2442000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>1885000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>1790000</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>9401000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>10363000</v>
+      </c>
+      <c r="F10" s="3">
         <v>9411000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>9201000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>8843000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>10106000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>8959000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>8917000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>8408000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>9443000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>8295000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>8201000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>7625000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>9105000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>8170000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>7861000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>7487000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>8470000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>7832000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>7566000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>7261000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>9074000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>7638000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>7561000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>7240000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>8841000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>6795000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>6746000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>6327000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>8451000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>7320000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>7245000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1093,103 +1117,111 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>2248000</v>
+        <v>2306000</v>
       </c>
       <c r="E12" s="3">
         <v>2226000</v>
       </c>
       <c r="F12" s="3">
-        <v>2216000</v>
+        <v>2248000</v>
       </c>
       <c r="G12" s="3">
         <v>2226000</v>
       </c>
       <c r="H12" s="3">
+        <v>2216000</v>
+      </c>
+      <c r="I12" s="3">
+        <v>2226000</v>
+      </c>
+      <c r="J12" s="3">
         <v>2146000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>2158000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>2093000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>1965000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>1816000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1754000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1684000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>1715000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>1928000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>1601000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>1589000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>1479000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>1500000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>1531000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>1557000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>1562000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>1426000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>1475000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>1564000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>1543000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>1496000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>1473000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>1572000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>1608000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>1521000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>1510000</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1283,198 +1315,216 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>86000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>193000</v>
+      </c>
+      <c r="F14" s="3">
         <v>245000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>130000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>149000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>181000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>115000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>199000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>185000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>108000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>39000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>4699000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>59000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>125000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>79000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>172000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>193000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>81000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>67000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>54000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>103000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>183000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>39000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>161000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>104000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>102000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>94000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>309000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>136000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>136000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>191000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AI14" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>624000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>743000</v>
+      </c>
+      <c r="F15" s="3">
         <v>749000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>755000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>763000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>870000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>886000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>907000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>919000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>268000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>279000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>299000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>303000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>342000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>347000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>345000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>345000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>365000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>400000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>407000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>414000</v>
-      </c>
-      <c r="W15" s="3">
-        <v>424000</v>
-      </c>
-      <c r="X15" s="3">
-        <v>407000</v>
       </c>
       <c r="Y15" s="3">
         <v>424000</v>
       </c>
       <c r="Z15" s="3">
+        <v>407000</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>424000</v>
+      </c>
+      <c r="AB15" s="3">
         <v>434000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>415000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>394000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>400000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>411000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>441000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>397000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AI15" s="3">
         <v>302000</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1505,198 +1555,212 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>9316000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>9601000</v>
+      </c>
+      <c r="F17" s="3">
         <v>9530000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>9319000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>9157000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>9696000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>9138000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>9204000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>8822000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>7338000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>6691000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>11184000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>6301000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>6686000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>6207000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>6217000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>6156000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>6131000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>6268000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>6431000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>6341000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>6880000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>6215000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>6461000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>6415000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>6853000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>6361000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>6550000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>6355000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>6819000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>6246000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>5998000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>3991000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>4686000</v>
+      </c>
+      <c r="F18" s="3">
         <v>3750000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>3622000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>3296000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>4140000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>3260000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>3071000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>2623000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>4502000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>3822000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-824000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>3427000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>4541000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>3878000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>3583000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>3211000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>4308000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>3528000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>3183000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>2877000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>4257000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>3399000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>3101000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>2778000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>4161000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>3315000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>3039000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>2749000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>4074000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>2959000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>3037000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1730,483 +1794,515 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-9000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-14000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-49000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-76000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-134000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-71000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-180000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-174000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-315000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>7000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-41000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>312000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-17000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-11000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-2000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-33000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>4000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>92000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>99000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>134000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>198000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>192000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>291000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>294000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>409000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>262000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>220000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>168000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>189000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>99000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>5439000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>6214000</v>
+      </c>
+      <c r="F21" s="3">
         <v>5298000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>5161000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>4722000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>5650000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>4684000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>4498000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>3909000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>5159000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>4282000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-58000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>4143000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>5605000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>4593000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>4303000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>3910000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>4997000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>4280000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>4023000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>3726000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>5145000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>4338000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>3997000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>3789000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>5157000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>4423000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>3989000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>3665000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>4961000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>3804000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>3679000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>842000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>878000</v>
+      </c>
+      <c r="F22" s="3">
         <v>876000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>888000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>872000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>955000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>908000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>856000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>787000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>704000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>667000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>679000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>705000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>697000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>585000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>600000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>614000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>579000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>456000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>465000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>494000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>525000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>509000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>519000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>529000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>548000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>533000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>475000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>469000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>481000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>450000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>451000</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>3169000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>3782000</v>
+      </c>
+      <c r="F23" s="3">
         <v>2865000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>2720000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>2375000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>3109000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>2218000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>2144000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>1656000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>3624000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>2840000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-1496000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>2681000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>4156000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>3276000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>2972000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>2595000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>3696000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>3076000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>2810000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>2482000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>3866000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>3088000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>2774000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>2540000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>3907000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>3191000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>2826000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>2500000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>3761000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>2698000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>2685000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>240000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>638000</v>
+      </c>
+      <c r="F24" s="3">
         <v>464000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>217000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-45000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-210000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>322000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>403000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>108000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>435000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>521000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-249000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>224000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>124000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-1745000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>530000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>344000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>580000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>505000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>499000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>345000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>126000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>579000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>441000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>428000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>632000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>367000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>612000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>356000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>529000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>459000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>653000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2300,198 +2396,216 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>2929000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>3144000</v>
+      </c>
+      <c r="F26" s="3">
         <v>2401000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>2503000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>2420000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>3319000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1896000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>1741000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>1548000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>3189000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>2319000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-1247000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>2457000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>4032000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>5021000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>2442000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>2251000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>3116000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>2571000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>2311000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>2137000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>3740000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>2509000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>2333000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>2112000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>3275000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>2824000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>2214000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>2144000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>3232000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>2239000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>2032000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>2929000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>3144000</v>
+      </c>
+      <c r="F27" s="3">
         <v>2401000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>2503000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>2420000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>3319000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1896000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>1741000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>1548000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>3189000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>2319000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1247000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>2457000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>4032000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>5021000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>2442000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>2251000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>3116000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>2571000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>2311000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>2137000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>3740000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>2509000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>2333000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>2112000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>3275000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>2824000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>2214000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>2144000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>3232000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>2239000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>2032000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2585,8 +2699,14 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2632,15 +2752,15 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
       <c r="U29" s="3">
         <v>0</v>
       </c>
@@ -2651,37 +2771,43 @@
         <v>0</v>
       </c>
       <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>236000</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>153000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AC29" s="3">
         <v>1000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AD29" s="3">
         <v>-6871000</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD29" s="3">
-        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>24</v>
+      <c r="AF29" s="3">
+        <v>0</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2775,8 +2901,14 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2870,198 +3002,216 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>26000</v>
+      </c>
+      <c r="F32" s="3">
         <v>9000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>14000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>49000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>76000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>134000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>71000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>180000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>174000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>315000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-7000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>41000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-312000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>17000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>11000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>2000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>33000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-4000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-92000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-99000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-134000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-198000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-192000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-291000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-294000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-409000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-262000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-220000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-168000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-189000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-99000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2929000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>3144000</v>
+      </c>
+      <c r="F33" s="3">
         <v>2401000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>2503000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>2420000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>3319000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1896000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>1741000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>1548000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>3189000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>2319000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1247000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>2457000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>4032000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>5021000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>2442000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>2251000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>3116000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>2571000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>2311000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>2137000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>3740000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>2745000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>2333000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>2265000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>3276000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-4047000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>2214000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>2144000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>3232000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>2239000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>2032000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3155,203 +3305,221 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2929000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>3144000</v>
+      </c>
+      <c r="F35" s="3">
         <v>2401000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>2503000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>2420000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>3319000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1896000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>1741000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>1548000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>3189000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>2319000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1247000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>2457000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>4032000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>5021000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>2442000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>2251000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>3116000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>2571000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>2311000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>2137000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>3740000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>2745000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>2333000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>2265000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>3276000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-4047000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>2214000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>2144000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>3232000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>2239000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>2032000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45535</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45443</v>
+      </c>
+      <c r="F38" s="2">
         <v>45351</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45260</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45169</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45077</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44985</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44895</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44804</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44712</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44620</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44530</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44439</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44347</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44255</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44165</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44074</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43982</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43890</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43799</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43708</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43616</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43524</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43434</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43343</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43251</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43159</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43069</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42978</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42886</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42794</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42704</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3385,8 +3553,10 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3420,293 +3590,313 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10616000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>10454000</v>
+      </c>
+      <c r="F41" s="3">
         <v>9481000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>8244000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>11613000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>9765000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>8219000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>6813000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>10448000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>21383000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>22682000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>17938000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>23059000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>30098000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>22321000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>28001000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>27276000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>37239000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>23829000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>24540000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>31083000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>20514000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>14720000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>10824000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>18455000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>21620000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>19487000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>21310000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>21321000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>21784000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>19748000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>18592000</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>295000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>207000</v>
+      </c>
+      <c r="F42" s="3">
         <v>423000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>446000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>470000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>422000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>550000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>537000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>772000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>519000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>707000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>4900000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>16251000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>16456000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>13543000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>10592000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>15003000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>5818000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>2029000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>2904000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>4621000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>17313000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>25310000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>38567000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>41639000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>45641000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>50968000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>50270000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>45576000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>44294000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>39604000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>39614000</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8021000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>7874000</v>
+      </c>
+      <c r="F43" s="3">
         <v>7297000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>6804000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>6519000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>6915000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>6213000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>6197000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>5937000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>5953000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>4588000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>4462000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>4482000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>5409000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>4637000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>4423000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>4576000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>6329000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>4162000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>4050000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>3820000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>5910000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>3993000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>3975000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>3729000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>5938000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>3902000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>3798000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>3591000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>5300000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>3721000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>3690000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3746,252 +3936,270 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q44" s="3" t="s">
-        <v>24</v>
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
       </c>
       <c r="R44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="S44" s="3">
-        <v>211000</v>
+      <c r="S44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="T44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>24</v>
+      <c r="U44" s="3">
+        <v>211000</v>
       </c>
       <c r="V44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="W44" s="3">
-        <v>320000</v>
+      <c r="W44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="X44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>24</v>
+      <c r="Y44" s="3">
+        <v>320000</v>
       </c>
       <c r="Z44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AA44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC44" s="3">
         <v>398000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>496000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>436000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>312000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>300000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>391000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4140000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>4019000</v>
+      </c>
+      <c r="F45" s="3">
         <v>3862000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>3795000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>3564000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>3902000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>3714000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>4014000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>3847000</v>
-      </c>
-      <c r="K45" s="3">
-        <v>3778000</v>
-      </c>
-      <c r="L45" s="3">
-        <v>3698000</v>
       </c>
       <c r="M45" s="3">
         <v>3778000</v>
       </c>
       <c r="N45" s="3">
+        <v>3698000</v>
+      </c>
+      <c r="O45" s="3">
+        <v>3778000</v>
+      </c>
+      <c r="P45" s="3">
         <v>3325000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>3604000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>3243000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>3235000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>3084000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>2543000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>3422000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>3046000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>2860000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>2329000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>3594000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>3572000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>3186000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>5986000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>2879000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>2731000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>2535000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>2837000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>2547000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>2511000</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>23072000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>22554000</v>
+      </c>
+      <c r="F46" s="3">
         <v>21063000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>19289000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>22166000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>21004000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>18696000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>17561000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>21004000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>31633000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>31675000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>31078000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>47117000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>55567000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>43744000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>46251000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>49939000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>52140000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>33442000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>34540000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>42384000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>46386000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>47617000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>56938000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>67009000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>76159000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>77732000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>78545000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>73335000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>74515000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>66011000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>64734000</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4085,198 +4293,216 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23094000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>21536000</v>
+      </c>
+      <c r="F48" s="3">
         <v>19117000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>18009000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>17644000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>17069000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>16345000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>14351000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>12280000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>9716000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>8609000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>8029000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>7610000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>7049000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>6816000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>6627000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>6401000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>9044000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>8048000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>8170000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>8264000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>6252000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>6197000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>6003000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>5918000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>5897000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>5904000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>5868000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>5586000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>5315000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>5070000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>4882000</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>68519000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>69120000</v>
+      </c>
+      <c r="F49" s="3">
         <v>69851000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>70609000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>71280000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>72098000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>72206000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>73106000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>74128000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>45251000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>45521000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>45723000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>46043000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>46365000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>46708000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>46938000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>47272000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>47507000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>47869000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>48302000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>48594000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>49058000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>49454000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>49881000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>49997000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>50425000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>49365000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>49758000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>50206000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>50724000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>50292000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>50051000</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4370,8 +4596,14 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4465,103 +4697,115 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>29529000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>27766000</v>
+      </c>
+      <c r="F52" s="3">
         <v>27051000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>26417000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>25572000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>24213000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>24373000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>23451000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>22897000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>22697000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>22839000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>22067000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>22154000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>22126000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>20841000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>10198000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>9934000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>6747000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>7345000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>7431000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>6987000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>7013000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>6170000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>5496000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>5434000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>5370000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>5200000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>4591000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>4470000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>4437000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>4009000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>3933000</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4655,103 +4899,115 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>144214000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>140976000</v>
+      </c>
+      <c r="F54" s="3">
         <v>137082000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>134324000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>136662000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>134384000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>131620000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>128469000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>130309000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>109297000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>108644000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>106897000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>122924000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>131107000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>118109000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>110014000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>113546000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>115438000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>96704000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>98443000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>106229000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>108709000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>109438000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>118318000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>128358000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>137851000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>138201000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>138762000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>133597000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>134991000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>125382000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>123600000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4785,8 +5041,10 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4820,578 +5078,616 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2207000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2357000</v>
+      </c>
+      <c r="F57" s="3">
         <v>1658000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1107000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1034000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1204000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1610000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1647000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1461000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1317000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1124000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1034000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>749000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>745000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>812000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>724000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>534000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>637000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>533000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>534000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>486000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>580000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>603000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>587000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>527000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>529000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>603000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>554000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>593000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>599000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>481000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>615000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9201000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>10605000</v>
+      </c>
+      <c r="F58" s="3">
         <v>5510000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>6321000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>4499000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>4061000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>5415000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>9746000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>16097000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>3749000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>6248000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>4998000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>6748000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>8250000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>5758000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>7251000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>2997000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>2371000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>2355000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>999000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>3748000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>4494000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>4487000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>6477000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>3743000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>4491000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>4491000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>2499000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>4998000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>9797000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>3498000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>3838000</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20637000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>18582000</v>
+      </c>
+      <c r="F59" s="3">
         <v>17717000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>16979000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>19824000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>17825000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>15855000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>15713000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>17261000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>14445000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>13461000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>12849000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>15574000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>15169000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>13680000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>13372000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>15217000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>14192000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>12852000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>13059000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>14641000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>13556000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>12896000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>13251000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>15292000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>14104000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>12874000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>12441000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>14635000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>13782000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>11811000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>11894000</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>32045000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>31544000</v>
+      </c>
+      <c r="F60" s="3">
         <v>24885000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>24407000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>25357000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>23090000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>22880000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>27106000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>34819000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>19511000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>20833000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>18881000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>23071000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>24164000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>20250000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>21347000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>18748000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>17200000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>15740000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>14592000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>18875000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>18630000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>17986000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>20315000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>19562000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>19124000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>17968000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>15494000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>20226000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>24178000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>15790000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>16347000</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>75314000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>76264000</v>
+      </c>
+      <c r="F61" s="3">
         <v>82470000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>82468000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>84442000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>86420000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>86396000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>81173000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>75480000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>72110000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>72165000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>73433000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>75970000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>75995000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>63541000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>63531000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>67769000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>69209000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>49299000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>50643000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>50684000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>51656000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>51672000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>51561000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>54386000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>56128000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>55145000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>57119000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>47355000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>47132000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>49518000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>51427000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>25586000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>23929000</v>
+      </c>
+      <c r="F62" s="3">
         <v>23545000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>23071000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>24022000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>23318000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>24256000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>23966000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>25459000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>23444000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>23857000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>24241000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>25013000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>24996000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>24681000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>16520000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>16889000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>16312000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>16784000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>17023000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>17651000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>16060000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>15542000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>15387000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>15846000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>15726000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>16816000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>9849000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>9650000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>9435000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>9051000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>6981000</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5485,8 +5781,14 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5580,8 +5882,14 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5675,103 +5983,115 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>133398000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>132272000</v>
+      </c>
+      <c r="F66" s="3">
         <v>131459000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>130458000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>134292000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>133311000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>134041000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>132715000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>136184000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>115517000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>117340000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>116998000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>124465000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>125869000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>109209000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>102097000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>104055000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>103364000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>82469000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>82880000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>87796000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>86924000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>85724000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>87746000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>90291000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>91479000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>90412000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>82894000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>77638000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>81131000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>74767000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>75138000</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5805,8 +6125,10 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5900,8 +6222,14 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5995,8 +6323,14 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6090,8 +6424,14 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6185,103 +6525,115 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-20939000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-22628000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-24533000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-25431000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-26428000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-27620000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-29721000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-30617000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-31134000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-31336000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-33147000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-34076000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-25679000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-20120000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-16206000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-17095000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-15410000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-12696000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-10771000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-9174000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-6446000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-3496000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-1284000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>5107000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>12022000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>19111000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>20037000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>28296000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>28586000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>27598000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>25576000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>24375000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6375,8 +6727,14 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6470,8 +6828,14 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6565,103 +6929,115 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10816000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>8704000</v>
+      </c>
+      <c r="F76" s="3">
         <v>5623000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3866000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2370000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1073000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-2421000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-4246000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-5875000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-6220000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-8696000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-10101000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-1541000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>5238000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>8900000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>7917000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>9491000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>12074000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>14235000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>15563000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>18433000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>21785000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>23714000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>30572000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>38067000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>46372000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>47789000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>55868000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>55959000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>53860000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>50615000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>48462000</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6755,203 +7131,221 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45535</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45443</v>
+      </c>
+      <c r="F80" s="2">
         <v>45351</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45260</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45169</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45077</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44985</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44895</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44804</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44712</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44620</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44530</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44439</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44347</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44255</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44165</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44074</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43982</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43890</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43799</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43708</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43616</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43524</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43434</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43343</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43251</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43159</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43069</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42978</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42886</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42794</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42704</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2929000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>3144000</v>
+      </c>
+      <c r="F81" s="3">
         <v>2401000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>2503000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>2420000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>3319000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1896000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>1741000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>1548000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>3189000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>2319000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1247000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>2457000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>4032000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>5021000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>2442000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>2251000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>3116000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>2571000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>2311000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>2137000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>3740000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>2745000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>2333000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>2265000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>3276000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-4047000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>2214000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>2144000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>3232000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>2239000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>2032000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6985,103 +7379,111 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1428000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1554000</v>
+      </c>
+      <c r="F83" s="3">
         <v>1557000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1553000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>1475000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>1586000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1558000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>1498000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>1466000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>831000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>775000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>759000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>757000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>752000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>732000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>731000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>701000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>722000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>748000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>748000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>750000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>754000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>741000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>704000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>720000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>702000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>699000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>688000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>696000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>719000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>656000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>543000</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7175,8 +7577,14 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7270,8 +7678,14 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7365,8 +7779,14 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7460,8 +7880,14 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7555,103 +7981,115 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7427000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>6081000</v>
+      </c>
+      <c r="F89" s="3">
         <v>5475000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>143000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>6974000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>5647000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>4275000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>849000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>6394000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>3985000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>3845000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-3682000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>5391000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>4842000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>3704000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>1388000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>5953000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>3614000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>3012000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>513000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>6000000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>4422000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>2861000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>546000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>6722000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>4660000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>3310000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>850000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>6566000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>4466000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>2699000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>1086000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7685,103 +8123,111 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2303000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-2798000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1674000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1080000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1314000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1913000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-2628000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-2435000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1719000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1423000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1101000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-925000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-1062000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-717000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-414000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-568000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-436000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-433000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-396000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-349000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-386000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-413000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-443000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-421000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-383000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-378000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-286000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-599000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-473000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-525000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-440000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-757000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7875,8 +8321,14 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7970,103 +8422,115 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2765000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-2766000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1783000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1249000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-1562000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1612000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-2778000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-2658000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-29436000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-1161000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>2432000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>10730000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-781000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-3911000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-3384000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>3852000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-9655000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-4256000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>480000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>1233000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>12386000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>7906000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>13199000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>1920000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>3532000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>3160000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-1257000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-5710000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-1818000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-5846000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-728000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-9717000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8100,103 +8564,111 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-1103000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>-1102000</v>
+      </c>
+      <c r="F96" s="3">
         <v>-1099000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>-1099000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>-1091000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>-1082000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>-863000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>-863000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>-860000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-854000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-855000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-861000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-887000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-917000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-699000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-717000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-730000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-740000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-768000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-767000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-795000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-806000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-670000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-714000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-742000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-778000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-783000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-791000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-788000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-787000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-612000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AI96" s="3">
         <v>-614000</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8290,8 +8762,14 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8385,8 +8863,14 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8480,289 +8964,313 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4585000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-2274000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-2463000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-2289000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-3528000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-2440000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-105000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-1855000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>12310000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-4026000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-1579000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-12053000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-11468000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>6798000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-6129000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-4554000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-6493000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>14133000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-4169000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-8294000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-7802000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-6461000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-12239000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-10023000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-13333000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-5459000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-4020000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>4938000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-5441000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>3287000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-940000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-973000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>85000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-68000</v>
+      </c>
+      <c r="F101" s="3">
         <v>8000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>26000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-36000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-49000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>14000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>29000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-203000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-97000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>46000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-116000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-181000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>48000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>129000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>39000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>232000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-81000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-34000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>5000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-15000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-73000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>75000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-74000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-86000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-228000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>144000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-89000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>230000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>129000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>125000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>-418000</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>162000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>973000</v>
+      </c>
+      <c r="F102" s="3">
         <v>1237000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-3369000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>1848000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>1546000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>1406000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-3635000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-10935000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1299000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>4744000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-5121000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-7039000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>7777000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-5680000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>725000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-9963000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>13410000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-711000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-6543000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>10569000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>5794000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>3896000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-7631000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-3165000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>2133000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-1823000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-463000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>2036000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>1156000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-10022000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ORCL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ORCL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
   <si>
     <t>ORCL</t>
   </si>
@@ -1327,25 +1327,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>86000</v>
+        <v>139000</v>
       </c>
       <c r="E14" s="3">
+        <v>79000</v>
+      </c>
+      <c r="F14" s="3">
         <v>193000</v>
       </c>
-      <c r="F14" s="3">
-        <v>245000</v>
-      </c>
       <c r="G14" s="3">
-        <v>130000</v>
+        <v>180000</v>
       </c>
       <c r="H14" s="3">
-        <v>149000</v>
+        <v>263000</v>
       </c>
       <c r="I14" s="3">
-        <v>181000</v>
+        <v>234000</v>
       </c>
       <c r="J14" s="3">
-        <v>115000</v>
+        <v>217000</v>
       </c>
       <c r="K14" s="3">
         <v>199000</v>
@@ -1563,25 +1563,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>9316000</v>
+        <v>9246000</v>
       </c>
       <c r="E17" s="3">
-        <v>9601000</v>
+        <v>9535000</v>
       </c>
       <c r="F17" s="3">
-        <v>9530000</v>
+        <v>9431000</v>
       </c>
       <c r="G17" s="3">
-        <v>9319000</v>
+        <v>9218000</v>
       </c>
       <c r="H17" s="3">
-        <v>9157000</v>
+        <v>9012000</v>
       </c>
       <c r="I17" s="3">
-        <v>9696000</v>
+        <v>9540000</v>
       </c>
       <c r="J17" s="3">
-        <v>9138000</v>
+        <v>9043000</v>
       </c>
       <c r="K17" s="3">
         <v>9204000</v>
@@ -1664,25 +1664,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>3991000</v>
+        <v>4061000</v>
       </c>
       <c r="E18" s="3">
-        <v>4686000</v>
+        <v>4752000</v>
       </c>
       <c r="F18" s="3">
-        <v>3750000</v>
+        <v>3849000</v>
       </c>
       <c r="G18" s="3">
-        <v>3622000</v>
+        <v>3723000</v>
       </c>
       <c r="H18" s="3">
-        <v>3296000</v>
+        <v>3441000</v>
       </c>
       <c r="I18" s="3">
-        <v>4140000</v>
+        <v>4296000</v>
       </c>
       <c r="J18" s="3">
-        <v>3260000</v>
+        <v>3355000</v>
       </c>
       <c r="K18" s="3">
         <v>3071000</v>
@@ -1802,25 +1802,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>20000</v>
+        <v>44000</v>
       </c>
       <c r="E20" s="3">
-        <v>-26000</v>
+        <v>84000</v>
       </c>
       <c r="F20" s="3">
-        <v>-9000</v>
+        <v>26000</v>
       </c>
       <c r="G20" s="3">
-        <v>-14000</v>
+        <v>68000</v>
       </c>
       <c r="H20" s="3">
-        <v>-49000</v>
+        <v>67000</v>
       </c>
       <c r="I20" s="3">
-        <v>-76000</v>
+        <v>103000</v>
       </c>
       <c r="J20" s="3">
-        <v>-134000</v>
+        <v>102000</v>
       </c>
       <c r="K20" s="3">
         <v>-71000</v>
@@ -1903,25 +1903,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>5439000</v>
+        <v>4641000</v>
       </c>
       <c r="E21" s="3">
-        <v>6214000</v>
+        <v>5411000</v>
       </c>
       <c r="F21" s="3">
-        <v>5298000</v>
+        <v>4572000</v>
       </c>
       <c r="G21" s="3">
-        <v>5161000</v>
+        <v>4410000</v>
       </c>
       <c r="H21" s="3">
-        <v>4722000</v>
+        <v>4137000</v>
       </c>
       <c r="I21" s="3">
-        <v>5650000</v>
+        <v>5063000</v>
       </c>
       <c r="J21" s="3">
-        <v>4684000</v>
+        <v>4139000</v>
       </c>
       <c r="K21" s="3">
         <v>4498000</v>
@@ -3014,25 +3014,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-20000</v>
+        <v>-44000</v>
       </c>
       <c r="E32" s="3">
-        <v>26000</v>
+        <v>-84000</v>
       </c>
       <c r="F32" s="3">
-        <v>9000</v>
+        <v>-26000</v>
       </c>
       <c r="G32" s="3">
-        <v>14000</v>
+        <v>-68000</v>
       </c>
       <c r="H32" s="3">
-        <v>49000</v>
+        <v>-67000</v>
       </c>
       <c r="I32" s="3">
-        <v>76000</v>
+        <v>-103000</v>
       </c>
       <c r="J32" s="3">
-        <v>134000</v>
+        <v>-102000</v>
       </c>
       <c r="K32" s="3">
         <v>71000</v>
@@ -3803,7 +3803,7 @@
         <v>8021000</v>
       </c>
       <c r="E43" s="3">
-        <v>7874000</v>
+        <v>8695000</v>
       </c>
       <c r="F43" s="3">
         <v>7297000</v>
@@ -3815,7 +3815,7 @@
         <v>6519000</v>
       </c>
       <c r="I43" s="3">
-        <v>6915000</v>
+        <v>7713000</v>
       </c>
       <c r="J43" s="3">
         <v>6213000</v>
@@ -3900,26 +3900,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
+        <v>334000</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+        <v>298000</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4001,26 +4001,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>4140000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>4019000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>3862000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>3795000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>3564000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>3902000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>3714000</v>
+      <c r="D45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="K45" s="3">
         <v>4014000</v>
@@ -4204,25 +4204,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>2300000</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>1900000</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>1800000</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>1700000</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>1600000</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>2100000</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4308,7 +4308,7 @@
         <v>23094000</v>
       </c>
       <c r="E48" s="3">
-        <v>21536000</v>
+        <v>28836000</v>
       </c>
       <c r="F48" s="3">
         <v>19117000</v>
@@ -4709,25 +4709,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>29529000</v>
+        <v>15010000</v>
       </c>
       <c r="E52" s="3">
-        <v>27766000</v>
+        <v>6193000</v>
       </c>
       <c r="F52" s="3">
-        <v>27051000</v>
+        <v>12463000</v>
       </c>
       <c r="G52" s="3">
-        <v>26417000</v>
+        <v>11859000</v>
       </c>
       <c r="H52" s="3">
-        <v>25572000</v>
+        <v>11629000</v>
       </c>
       <c r="I52" s="3">
-        <v>24213000</v>
+        <v>10387000</v>
       </c>
       <c r="J52" s="3">
-        <v>24373000</v>
+        <v>10120000</v>
       </c>
       <c r="K52" s="3">
         <v>23451000</v>
@@ -5190,7 +5190,7 @@
         <v>9201000</v>
       </c>
       <c r="E58" s="3">
-        <v>10605000</v>
+        <v>11905000</v>
       </c>
       <c r="F58" s="3">
         <v>5510000</v>
@@ -5288,25 +5288,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>20637000</v>
+        <v>18865000</v>
       </c>
       <c r="E59" s="3">
-        <v>18582000</v>
+        <v>15366000</v>
       </c>
       <c r="F59" s="3">
-        <v>17717000</v>
+        <v>15921000</v>
       </c>
       <c r="G59" s="3">
-        <v>16979000</v>
+        <v>15273000</v>
       </c>
       <c r="H59" s="3">
-        <v>19824000</v>
+        <v>18006000</v>
       </c>
       <c r="I59" s="3">
-        <v>17825000</v>
+        <v>15772000</v>
       </c>
       <c r="J59" s="3">
-        <v>15855000</v>
+        <v>14119000</v>
       </c>
       <c r="K59" s="3">
         <v>15713000</v>
@@ -5493,7 +5493,7 @@
         <v>75314000</v>
       </c>
       <c r="E61" s="3">
-        <v>76264000</v>
+        <v>82509000</v>
       </c>
       <c r="F61" s="3">
         <v>82470000</v>
@@ -5591,25 +5591,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>25586000</v>
+        <v>20715000</v>
       </c>
       <c r="E62" s="3">
-        <v>23929000</v>
+        <v>12759000</v>
       </c>
       <c r="F62" s="3">
-        <v>23545000</v>
+        <v>17797000</v>
       </c>
       <c r="G62" s="3">
-        <v>23071000</v>
+        <v>16576000</v>
       </c>
       <c r="H62" s="3">
-        <v>24022000</v>
+        <v>17595000</v>
       </c>
       <c r="I62" s="3">
-        <v>23318000</v>
+        <v>16578000</v>
       </c>
       <c r="J62" s="3">
-        <v>24256000</v>
+        <v>16652000</v>
       </c>
       <c r="K62" s="3">
         <v>23966000</v>
@@ -5995,25 +5995,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>133398000</v>
+        <v>132945000</v>
       </c>
       <c r="E66" s="3">
-        <v>132272000</v>
+        <v>131737000</v>
       </c>
       <c r="F66" s="3">
-        <v>131459000</v>
+        <v>130900000</v>
       </c>
       <c r="G66" s="3">
-        <v>130458000</v>
+        <v>129946000</v>
       </c>
       <c r="H66" s="3">
-        <v>134292000</v>
+        <v>133821000</v>
       </c>
       <c r="I66" s="3">
-        <v>133311000</v>
+        <v>132828000</v>
       </c>
       <c r="J66" s="3">
-        <v>134041000</v>
+        <v>133532000</v>
       </c>
       <c r="K66" s="3">
         <v>132715000</v>
@@ -7387,25 +7387,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1428000</v>
+        <v>712000</v>
       </c>
       <c r="E83" s="3">
-        <v>1554000</v>
+        <v>716000</v>
       </c>
       <c r="F83" s="3">
-        <v>1557000</v>
+        <v>672000</v>
       </c>
       <c r="G83" s="3">
-        <v>1553000</v>
+        <v>591000</v>
       </c>
       <c r="H83" s="3">
-        <v>1475000</v>
+        <v>547000</v>
       </c>
       <c r="I83" s="3">
-        <v>1586000</v>
+        <v>563000</v>
       </c>
       <c r="J83" s="3">
-        <v>1558000</v>
+        <v>496000</v>
       </c>
       <c r="K83" s="3">
         <v>1498000</v>
@@ -8572,25 +8572,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1103000</v>
+        <v>1103000</v>
       </c>
       <c r="E96" s="3">
-        <v>-1102000</v>
+        <v>1102000</v>
       </c>
       <c r="F96" s="3">
-        <v>-1099000</v>
+        <v>1099000</v>
       </c>
       <c r="G96" s="3">
-        <v>-1099000</v>
+        <v>1099000</v>
       </c>
       <c r="H96" s="3">
-        <v>-1091000</v>
+        <v>1091000</v>
       </c>
       <c r="I96" s="3">
-        <v>-1082000</v>
+        <v>1082000</v>
       </c>
       <c r="J96" s="3">
-        <v>-863000</v>
+        <v>863000</v>
       </c>
       <c r="K96" s="3">
         <v>-863000</v>
@@ -9077,25 +9077,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>85000</v>
+        <v>-36000</v>
       </c>
       <c r="E101" s="3">
-        <v>-68000</v>
+        <v>-49000</v>
       </c>
       <c r="F101" s="3">
-        <v>8000</v>
+        <v>14000</v>
       </c>
       <c r="G101" s="3">
-        <v>26000</v>
+        <v>29000</v>
       </c>
       <c r="H101" s="3">
-        <v>-36000</v>
+        <v>-203000</v>
       </c>
       <c r="I101" s="3">
-        <v>-49000</v>
+        <v>-97000</v>
       </c>
       <c r="J101" s="3">
-        <v>14000</v>
+        <v>46000</v>
       </c>
       <c r="K101" s="3">
         <v>29000</v>

--- a/AAII_Financials/Quarterly/ORCL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ORCL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <si>
     <t>ORCL</t>
   </si>
@@ -656,434 +656,458 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="21" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45716</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45626</v>
+      </c>
+      <c r="F7" s="2">
         <v>45535</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45443</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45351</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45260</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45169</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45077</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44985</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44895</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44804</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44712</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44620</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44530</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44439</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44347</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44255</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44165</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44074</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43982</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43890</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43799</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43708</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43616</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43524</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43434</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43343</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43251</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43159</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43069</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42978</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42886</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42794</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42704</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>14130000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>14059000</v>
+      </c>
+      <c r="F8" s="3">
         <v>13307000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>14287000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>13280000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>12941000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>12453000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>13836000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>12398000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>12275000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>11445000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>11840000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>10513000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>10360000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>9728000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>11227000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>10085000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>9800000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>9367000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>10439000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>9796000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>9614000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>9218000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>11137000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>9614000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>9562000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>9193000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>11014000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>9676000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>9589000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>9104000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>10893000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>9205000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>9035000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4195000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>4085000</v>
+      </c>
+      <c r="F9" s="3">
         <v>3906000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>3924000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>3869000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>3740000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>3610000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>3730000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>3439000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>3358000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>3037000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>2397000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>2218000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>2159000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>2103000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>2122000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1915000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>1939000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1880000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>1969000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1964000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>2048000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1957000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>2063000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>1976000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>2001000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>1953000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>2173000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>2881000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>2843000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>2777000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>2442000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>1885000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>1790000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>9935000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>9974000</v>
+      </c>
+      <c r="F10" s="3">
         <v>9401000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>10363000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>9411000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>9201000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>8843000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>10106000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>8959000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>8917000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>8408000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>9443000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>8295000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>8201000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>7625000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>9105000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>8170000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>7861000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>7487000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>8470000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>7832000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>7566000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>7261000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>9074000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>7638000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>7561000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>7240000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>8841000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>6795000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>6746000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>6327000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>8451000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>7320000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>7245000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1119,109 +1143,117 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2429000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2471000</v>
+      </c>
+      <c r="F12" s="3">
         <v>2306000</v>
-      </c>
-      <c r="E12" s="3">
-        <v>2226000</v>
-      </c>
-      <c r="F12" s="3">
-        <v>2248000</v>
       </c>
       <c r="G12" s="3">
         <v>2226000</v>
       </c>
       <c r="H12" s="3">
-        <v>2216000</v>
+        <v>2248000</v>
       </c>
       <c r="I12" s="3">
         <v>2226000</v>
       </c>
       <c r="J12" s="3">
+        <v>2216000</v>
+      </c>
+      <c r="K12" s="3">
+        <v>2226000</v>
+      </c>
+      <c r="L12" s="3">
         <v>2146000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>2158000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>2093000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1965000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1816000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>1754000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>1684000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>1715000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>1928000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>1601000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>1589000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>1479000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>1500000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>1531000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>1557000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>1562000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>1426000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>1475000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>1564000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>1543000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>1496000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>1473000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>1572000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>1608000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>1521000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>1510000</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1321,210 +1353,228 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>123000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>192000</v>
+      </c>
+      <c r="F14" s="3">
         <v>139000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>79000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>193000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>180000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>263000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>234000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>217000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>199000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>185000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>108000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>39000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>4699000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>59000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>125000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>79000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>172000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>193000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>81000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>67000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>54000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>103000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>183000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>39000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>161000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>104000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>102000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>94000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>309000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>136000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AI14" s="3">
         <v>136000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AJ14" s="3">
         <v>191000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AK14" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>548000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>591000</v>
+      </c>
+      <c r="F15" s="3">
         <v>624000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>743000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>749000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>755000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>763000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>870000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>886000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>907000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>919000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>268000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>279000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>299000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>303000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>342000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>347000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>345000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>345000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>365000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>400000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>407000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>414000</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>424000</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>407000</v>
       </c>
       <c r="AA15" s="3">
         <v>424000</v>
       </c>
       <c r="AB15" s="3">
+        <v>407000</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>424000</v>
+      </c>
+      <c r="AD15" s="3">
         <v>434000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>415000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>394000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>400000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>411000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AI15" s="3">
         <v>441000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AJ15" s="3">
         <v>397000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AK15" s="3">
         <v>302000</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1557,210 +1607,224 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>9708000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>9755000</v>
+      </c>
+      <c r="F17" s="3">
         <v>9246000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>9535000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>9431000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>9218000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>9012000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>9540000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>9043000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>9204000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>8822000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>7338000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>6691000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>11184000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>6301000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>6686000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>6207000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>6217000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>6156000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>6131000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>6268000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>6431000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>6341000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>6880000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>6215000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>6461000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>6415000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>6853000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>6361000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>6550000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>6355000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>6819000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>6246000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>5998000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>4422000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>4304000</v>
+      </c>
+      <c r="F18" s="3">
         <v>4061000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>4752000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>3849000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>3723000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>3441000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>4296000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>3355000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>3071000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>2623000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>4502000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>3822000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-824000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>3427000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>4541000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>3878000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>3583000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>3211000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>4308000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>3528000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>3183000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>2877000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>4257000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>3399000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>3101000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>2778000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>4161000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>3315000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>3039000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>2749000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>4074000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>2959000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>3037000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1796,513 +1860,545 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>94000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F20" s="3">
         <v>44000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>84000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>26000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>68000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>67000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>103000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>102000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-71000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-180000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-174000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-315000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>7000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-41000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>312000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-17000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-11000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-2000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-33000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>4000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>92000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>99000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>134000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>198000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>192000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>291000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>294000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>409000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>262000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>220000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>168000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>189000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>99000</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>4876000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>4890000</v>
+      </c>
+      <c r="F21" s="3">
         <v>4641000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>5411000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>4572000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>4410000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>4137000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>5063000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>4139000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>4498000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>3909000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>5159000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>4282000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-58000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>4143000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>5605000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>4593000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>4303000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>3910000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>4997000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>4280000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>4023000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>3726000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>5145000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>4338000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>3997000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>3789000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>5157000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>4423000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>3989000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>3665000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>4961000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>3804000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>3679000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>892000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>866000</v>
+      </c>
+      <c r="F22" s="3">
         <v>842000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>878000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>876000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>888000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>872000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>955000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>908000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>856000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>787000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>704000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>667000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>679000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>705000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>697000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>585000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>600000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>614000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>579000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>456000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>465000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>494000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>525000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>509000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>519000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>529000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>548000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>533000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>475000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>469000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>481000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>450000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>451000</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>3448000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>3390000</v>
+      </c>
+      <c r="F23" s="3">
         <v>3169000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>3782000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>2865000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>2720000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>2375000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>3109000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>2218000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>2144000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>1656000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>3624000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>2840000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-1496000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>2681000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>4156000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>3276000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>2972000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>2595000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>3696000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>3076000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>2810000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>2482000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>3866000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>3088000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>2774000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>2540000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>3907000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>3191000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>2826000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>2500000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>3761000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>2698000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>2685000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>512000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>239000</v>
+      </c>
+      <c r="F24" s="3">
         <v>240000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>638000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>464000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>217000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-45000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-210000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>322000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>403000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>108000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>435000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>521000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-249000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>224000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>124000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-1745000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>530000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>344000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>580000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>505000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>499000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>345000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>126000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>579000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>441000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>428000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>632000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>367000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>612000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>356000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>529000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>459000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>653000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2402,210 +2498,228 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>2936000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>3151000</v>
+      </c>
+      <c r="F26" s="3">
         <v>2929000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>3144000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>2401000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>2503000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>2420000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>3319000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>1896000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1741000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1548000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>3189000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>2319000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-1247000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>2457000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>4032000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>5021000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>2442000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>2251000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>3116000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>2571000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>2311000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>2137000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>3740000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>2509000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>2333000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>2112000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>3275000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>2824000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>2214000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>2144000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>3232000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>2239000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>2032000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>2936000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>3151000</v>
+      </c>
+      <c r="F27" s="3">
         <v>2929000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>3144000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>2401000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>2503000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>2420000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>3319000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>1896000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1741000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1548000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>3189000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>2319000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-1247000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>2457000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>4032000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>5021000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>2442000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>2251000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>3116000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>2571000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>2311000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>2137000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>3740000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>2509000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>2333000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>2112000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>3275000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>2824000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>2214000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>2144000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>3232000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>2239000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>2032000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2705,8 +2819,14 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2758,15 +2878,15 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
       <c r="W29" s="3">
         <v>0</v>
       </c>
@@ -2777,37 +2897,43 @@
         <v>0</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>236000</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>153000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AE29" s="3">
         <v>1000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AF29" s="3">
         <v>-6871000</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AF29" s="3">
-        <v>0</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>24</v>
+      <c r="AH29" s="3">
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AK29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2907,8 +3033,14 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3008,210 +3140,228 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-94000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-44000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-84000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-26000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-68000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-67000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-103000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-102000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>71000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>180000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>174000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>315000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-7000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>41000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-312000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>17000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>11000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>2000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>33000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-4000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-92000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-99000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-134000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-198000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-192000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-291000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-294000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-409000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-262000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-220000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-168000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-189000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-99000</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2936000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>3151000</v>
+      </c>
+      <c r="F33" s="3">
         <v>2929000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>3144000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>2401000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>2503000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>2420000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>3319000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>1896000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1741000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1548000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>3189000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>2319000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-1247000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>2457000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>4032000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>5021000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>2442000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>2251000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>3116000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>2571000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>2311000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>2137000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>3740000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>2745000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>2333000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>2265000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>3276000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-4047000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>2214000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>2144000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>3232000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>2239000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>2032000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3311,215 +3461,233 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2936000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>3151000</v>
+      </c>
+      <c r="F35" s="3">
         <v>2929000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>3144000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>2401000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>2503000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>2420000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>3319000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>1896000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1741000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1548000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>3189000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>2319000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-1247000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>2457000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>4032000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>5021000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>2442000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>2251000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>3116000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>2571000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>2311000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>2137000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>3740000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>2745000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>2333000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>2265000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>3276000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-4047000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>2214000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>2144000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>3232000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>2239000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>2032000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45716</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45626</v>
+      </c>
+      <c r="F38" s="2">
         <v>45535</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45443</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45351</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45260</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45169</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45077</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44985</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44895</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44804</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44712</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44620</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44530</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44439</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44347</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44255</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44165</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44074</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43982</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43890</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43799</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43708</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43616</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43524</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43434</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43343</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43251</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43159</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43069</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42978</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42886</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42794</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42704</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3555,8 +3723,10 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3592,340 +3762,360 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17406000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>10941000</v>
+      </c>
+      <c r="F41" s="3">
         <v>10616000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>10454000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>9481000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>8244000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>11613000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>9765000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>8219000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>6813000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>10448000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>21383000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>22682000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>17938000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>23059000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>30098000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>22321000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>28001000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>27276000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>37239000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>23829000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>24540000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>31083000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>20514000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>14720000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>10824000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>18455000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>21620000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>19487000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>21310000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>21321000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>21784000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>19748000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>18592000</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>417000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>370000</v>
+      </c>
+      <c r="F42" s="3">
         <v>295000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>207000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>423000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>446000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>470000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>422000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>550000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>537000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>772000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>519000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>707000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>4900000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>16251000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>16456000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>13543000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>10592000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>15003000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>5818000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>2029000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>2904000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>4621000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>17313000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>25310000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>38567000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>41639000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>45641000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>50968000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>50270000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>45576000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>44294000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AJ42" s="3">
         <v>39604000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AK42" s="3">
         <v>39614000</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8051000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>8177000</v>
+      </c>
+      <c r="F43" s="3">
         <v>8021000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>8695000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>7297000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>6804000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>6519000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>7713000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>6213000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>6197000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>5937000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>5953000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>4588000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>4462000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>4482000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>5409000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>4637000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>4423000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>4576000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>6329000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>4162000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>4050000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>3820000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>5910000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>3993000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>3975000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>3729000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>5938000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>3902000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>3798000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>3591000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>5300000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>3721000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>3690000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E44" s="3">
-        <v>334000</v>
+      <c r="E44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>24</v>
+      <c r="G44" s="3">
+        <v>334000</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I44" s="3">
-        <v>298000</v>
+      <c r="I44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>24</v>
       </c>
       <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+        <v>298000</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3942,62 +4132,68 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="S44" s="3" t="s">
-        <v>24</v>
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3">
+        <v>0</v>
       </c>
       <c r="T44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="U44" s="3">
-        <v>211000</v>
+      <c r="U44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="V44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>24</v>
+      <c r="W44" s="3">
+        <v>211000</v>
       </c>
       <c r="X44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y44" s="3">
-        <v>320000</v>
+      <c r="Y44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>24</v>
+      <c r="AA44" s="3">
+        <v>320000</v>
       </c>
       <c r="AB44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AC44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE44" s="3">
         <v>398000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>496000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>436000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>312000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>300000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>391000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4022,214 +4218,226 @@
       <c r="J45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M45" s="3">
         <v>4014000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>3847000</v>
-      </c>
-      <c r="M45" s="3">
-        <v>3778000</v>
-      </c>
-      <c r="N45" s="3">
-        <v>3698000</v>
       </c>
       <c r="O45" s="3">
         <v>3778000</v>
       </c>
       <c r="P45" s="3">
+        <v>3698000</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>3778000</v>
+      </c>
+      <c r="R45" s="3">
         <v>3325000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>3604000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>3243000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>3235000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>3084000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>2543000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>3422000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>3046000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>2860000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>2329000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>3594000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>3572000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>3186000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>5986000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>2879000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>2731000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>2535000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>2837000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>2547000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>2511000</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>30116000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>23503000</v>
+      </c>
+      <c r="F46" s="3">
         <v>23072000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>22554000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>21063000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>19289000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>22166000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>21004000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>18696000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>17561000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>21004000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>31633000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>31675000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>31078000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>47117000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>55567000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>43744000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>46251000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>49939000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>52140000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>33442000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>34540000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>42384000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>46386000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>47617000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>56938000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>67009000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>76159000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>77732000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>78545000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>73335000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>74515000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>66011000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>64734000</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>1900000</v>
+      </c>
+      <c r="F47" s="3">
         <v>2300000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>2000000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>1900000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>1800000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>1700000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>1600000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>2100000</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -4299,210 +4507,228 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>43670000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>26432000</v>
+      </c>
+      <c r="F48" s="3">
         <v>23094000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>28836000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>19117000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>18009000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>17644000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>17069000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>16345000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>14351000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>12280000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>9716000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>8609000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>8029000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>7610000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>7049000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>6816000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>6627000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>6401000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>9044000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>8048000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>8170000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>8264000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>6252000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>6197000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>6003000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>5918000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>5897000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>5904000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>5868000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>5586000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>5315000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>5070000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>4882000</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>67302000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>67883000</v>
+      </c>
+      <c r="F49" s="3">
         <v>68519000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>69120000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>69851000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>70609000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>71280000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>72098000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>72206000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>73106000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>74128000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>45251000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>45521000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>45723000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>46043000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>46365000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>46708000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>46938000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>47272000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>47507000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>47869000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>48302000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>48594000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>49058000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>49454000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>49881000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>49997000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>50425000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>49365000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>49758000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>50206000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>50724000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>50292000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>50051000</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4602,8 +4828,14 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4703,109 +4935,121 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6491000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>16781000</v>
+      </c>
+      <c r="F52" s="3">
         <v>15010000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>6193000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>12463000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>11859000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>11629000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>10387000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>10120000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>23451000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>22897000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>22697000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>22839000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>22067000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>22154000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>22126000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>20841000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>10198000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>9934000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>6747000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>7345000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>7431000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>6987000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>7013000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>6170000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>5496000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>5434000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>5370000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>5200000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>4591000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>4470000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>4437000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>4009000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>3933000</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4905,109 +5149,121 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>161378000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>148483000</v>
+      </c>
+      <c r="F54" s="3">
         <v>144214000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>140976000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>137082000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>134324000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>136662000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>134384000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>131620000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>128469000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>130309000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>109297000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>108644000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>106897000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>122924000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>131107000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>118109000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>110014000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>113546000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>115438000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>96704000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>98443000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>106229000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>108709000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>109438000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>118318000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>128358000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>137851000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>138201000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>138762000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>133597000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>134991000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>125382000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>123600000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5043,8 +5299,10 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5080,614 +5338,652 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2423000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2679000</v>
+      </c>
+      <c r="F57" s="3">
         <v>2207000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2357000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1658000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1107000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1034000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1204000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1610000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1647000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1461000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1317000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1124000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1034000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>749000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>745000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>812000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>724000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>534000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>637000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>533000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>534000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>486000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>580000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>603000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>587000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>527000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>529000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>603000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>554000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>593000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>599000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>481000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>615000</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8167000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>8162000</v>
+      </c>
+      <c r="F58" s="3">
         <v>9201000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>11905000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>5510000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>6321000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>4499000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>4061000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>5415000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>9746000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>16097000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>3749000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>6248000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>4998000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>6748000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>8250000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>5758000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>7251000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>2997000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>2371000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>2355000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>999000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>3748000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>4494000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>4487000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>6477000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>3743000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>4491000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>4491000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>2499000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>4998000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>9797000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>3498000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>3838000</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>17194000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>16558000</v>
+      </c>
+      <c r="F59" s="3">
         <v>18865000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>15366000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>15921000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>15273000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>18006000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>15772000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>14119000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>15713000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>17261000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>14445000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>13461000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>12849000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>15574000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>15169000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>13680000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>13372000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>15217000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>14192000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>12852000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>13059000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>14641000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>13556000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>12896000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>13251000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>15292000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>14104000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>12874000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>12441000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>14635000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>13782000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>11811000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>11894000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>29623000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>29052000</v>
+      </c>
+      <c r="F60" s="3">
         <v>32045000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>31544000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>24885000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>24407000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>25357000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>23090000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>22880000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>27106000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>34819000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>19511000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>20833000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>18881000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>23071000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>24164000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>20250000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>21347000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>18748000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>17200000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>15740000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>14592000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>18875000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>18630000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>17986000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>20315000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>19562000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>19124000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>17968000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>15494000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>20226000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>24178000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>15790000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>16347000</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>75314000</v>
+        <v>101009000</v>
       </c>
       <c r="E61" s="3">
+        <v>91382000</v>
+      </c>
+      <c r="F61" s="3">
+        <v>84991000</v>
+      </c>
+      <c r="G61" s="3">
         <v>82509000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>82470000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>82468000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>84442000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>86420000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>86396000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>81173000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>75480000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>72110000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>72165000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>73433000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>75970000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>75995000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>63541000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>63531000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>67769000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>69209000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>49299000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>50643000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>50684000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>51656000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>51672000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>51561000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>54386000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>56128000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>55145000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>57119000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>47355000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>47132000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>49518000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>51427000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>20715000</v>
+        <v>9928000</v>
       </c>
       <c r="E62" s="3">
+        <v>9553000</v>
+      </c>
+      <c r="F62" s="3">
+        <v>11038000</v>
+      </c>
+      <c r="G62" s="3">
         <v>12759000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>17797000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>16576000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>17595000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>16578000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>16652000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>23966000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>25459000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>23444000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>23857000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>24241000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>25013000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>24996000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>24681000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>16520000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>16889000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>16312000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>16784000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>17023000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>17651000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>16060000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>15542000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>15387000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>15846000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>15726000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>16816000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>9849000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>9650000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>9435000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>9051000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>6981000</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5787,8 +6083,14 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5888,8 +6190,14 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5989,109 +6297,121 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>144117000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>134247000</v>
+      </c>
+      <c r="F66" s="3">
         <v>132945000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>131737000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>130900000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>129946000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>133821000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>132828000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>133532000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>132715000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>136184000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>115517000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>117340000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>116998000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>124465000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>125869000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>109209000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>102097000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>104055000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>103364000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>82469000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>82880000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>87796000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>86924000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>85724000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>87746000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>90291000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>91479000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>90412000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>82894000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>77638000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>81131000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>74767000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>75138000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6127,8 +6447,10 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6228,8 +6550,14 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6329,8 +6657,14 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6430,8 +6764,14 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6531,109 +6871,121 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-17368000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-19045000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-20939000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-22628000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-24533000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-25431000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-26428000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-27620000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-29721000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-30617000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-31134000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-31336000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-33147000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-34076000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-25679000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-20120000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-16206000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-17095000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-15410000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-12696000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-10771000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-9174000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-6446000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-3496000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-1284000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>5107000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>12022000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>19111000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>20037000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>28296000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>28586000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>27598000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>25576000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>24375000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6733,8 +7085,14 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6834,8 +7192,14 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6935,109 +7299,121 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16730000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>13746000</v>
+      </c>
+      <c r="F76" s="3">
         <v>10816000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>8704000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5623000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>3866000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>2370000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1073000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-2421000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-4246000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-5875000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-6220000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-8696000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-10101000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-1541000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>5238000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>8900000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>7917000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>9491000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>12074000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>14235000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>15563000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>18433000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>21785000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>23714000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>30572000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>38067000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>46372000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>47789000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>55868000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>55959000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>53860000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>50615000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>48462000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7137,215 +7513,233 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45716</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45626</v>
+      </c>
+      <c r="F80" s="2">
         <v>45535</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45443</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45351</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45260</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45169</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45077</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44985</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44895</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44804</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44712</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44620</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44530</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44439</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44347</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44255</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44165</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44074</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43982</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43890</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43799</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43708</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43616</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43524</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43434</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43343</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43251</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43159</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43069</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42978</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42886</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42794</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42704</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2936000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>3151000</v>
+      </c>
+      <c r="F81" s="3">
         <v>2929000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>3144000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>2401000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>2503000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>2420000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>3319000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>1896000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1741000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1548000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>3189000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>2319000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-1247000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>2457000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>4032000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>5021000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>2442000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>2251000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>3116000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>2571000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>2311000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>2137000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>3740000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>2745000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>2333000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>2265000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>3276000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-4047000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>2214000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>2144000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>3232000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>2239000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>2032000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7381,109 +7775,117 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>808000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>798000</v>
+      </c>
+      <c r="F83" s="3">
         <v>712000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>716000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>672000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>591000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>547000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>563000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>496000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>1498000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>1466000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>831000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>775000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>759000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>757000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>752000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>732000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>731000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>701000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>722000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>748000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>748000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>750000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>754000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>741000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>704000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>720000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>702000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>699000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>688000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>696000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>719000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>656000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>543000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7583,8 +7985,14 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7684,8 +8092,14 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7785,8 +8199,14 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7886,8 +8306,14 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7987,109 +8413,121 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5933000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1304000</v>
+      </c>
+      <c r="F89" s="3">
         <v>7427000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>6081000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>5475000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>143000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>6974000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>5647000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>4275000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>849000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>6394000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>3985000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>3845000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-3682000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>5391000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>4842000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>3704000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>1388000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>5953000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>3614000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>3012000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>513000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>6000000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>4422000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>2861000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>546000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>6722000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>4660000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>3310000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>850000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>6566000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>4466000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>2699000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>1086000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8125,109 +8563,117 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5862000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-3970000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-2303000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-2798000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1674000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1080000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1314000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1913000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-2628000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-2435000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1719000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1423000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-1101000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-925000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1062000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-717000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-414000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-568000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-436000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-433000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-396000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-349000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-386000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-413000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-443000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-421000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-383000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-378000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-286000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-599000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-473000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-525000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-440000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-757000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8327,8 +8773,14 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8428,109 +8880,121 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5976000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-3788000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-2765000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-2766000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-1783000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1249000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-1562000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1612000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-2778000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-2658000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-29436000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1161000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>2432000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>10730000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-781000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-3911000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-3384000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>3852000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-9655000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-4256000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>480000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>1233000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>12386000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>7906000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>13199000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>1920000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>3532000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>3160000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-1257000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-5710000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-1818000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-5846000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-728000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-9717000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8566,109 +9030,117 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1119000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>1118000</v>
+      </c>
+      <c r="F96" s="3">
         <v>1103000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>1102000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>1099000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>1099000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>1091000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>1082000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>863000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-863000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-860000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-854000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-855000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-861000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-887000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-917000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-699000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-717000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-730000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-740000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-768000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-767000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-795000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-806000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-670000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-714000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-742000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-778000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-783000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-791000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-788000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AI96" s="3">
         <v>-787000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AJ96" s="3">
         <v>-612000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AK96" s="3">
         <v>-614000</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8768,8 +9240,14 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8869,8 +9347,14 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8970,307 +9454,331 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6559000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>2938000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-4585000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-2274000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-2463000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-2289000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-3528000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-2440000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-105000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1855000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>12310000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-4026000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-1579000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-12053000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-11468000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>6798000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-6129000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-4554000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-6493000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>14133000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-4169000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-8294000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-7802000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-6461000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-12239000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-10023000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-13333000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-5459000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-4020000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>4938000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-5441000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>3287000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-940000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-973000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>26000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-36000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-49000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>14000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>29000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-203000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-97000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>46000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>29000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-203000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-97000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>46000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-116000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-181000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>48000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>129000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>39000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>232000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-81000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-34000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>5000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-15000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-73000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>75000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-74000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-86000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-228000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>144000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-89000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>230000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>129000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>125000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-418000</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6465000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>325000</v>
+      </c>
+      <c r="F102" s="3">
         <v>162000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>973000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>1237000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-3369000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>1848000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>1546000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>1406000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-3635000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-10935000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1299000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>4744000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-5121000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-7039000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>7777000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-5680000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>725000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-9963000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>13410000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-711000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-6543000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>10569000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>5794000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>3896000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-7631000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-3165000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>2133000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-1823000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-11000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-463000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>2036000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>1156000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-10022000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ORCL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ORCL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
   <si>
     <t>ORCL</t>
   </si>
@@ -656,458 +656,470 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="24" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45808</v>
+      </c>
+      <c r="E7" s="2">
         <v>45716</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45626</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45535</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45443</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45351</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45260</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45169</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45077</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44985</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44895</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44804</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44712</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44620</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44530</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44439</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44347</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44255</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44165</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44074</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43982</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43890</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43799</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43708</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43616</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43524</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43434</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43343</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43251</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43159</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43069</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42978</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42886</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42794</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42704</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>15903000</v>
+      </c>
+      <c r="E8" s="3">
         <v>14130000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14059000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13307000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>14287000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13280000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>12941000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>12453000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13836000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12398000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12275000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11445000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11840000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>10513000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10360000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>9728000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11227000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10085000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>9800000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>9367000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>10439000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>9796000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>9614000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>9218000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>11137000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>9614000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>9562000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>9193000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>11014000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>9676000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>9589000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>9104000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>10893000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>9205000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>9035000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4741000</v>
+      </c>
+      <c r="E9" s="3">
         <v>4195000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4085000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3906000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3924000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3869000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3740000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3610000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3730000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3439000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3358000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3037000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2397000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2218000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2159000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2103000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2122000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1915000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1939000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1880000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1969000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1964000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2048000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1957000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2063000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1976000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2001000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1953000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2173000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2881000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2843000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2777000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2442000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1885000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1790000</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>11162000</v>
+      </c>
+      <c r="E10" s="3">
         <v>9935000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>9974000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9401000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>10363000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>9411000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>9201000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>8843000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10106000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8959000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8917000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8408000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>9443000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>8295000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>8201000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>7625000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>9105000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>8170000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>7861000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>7487000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>8470000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>7832000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>7566000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>7261000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>9074000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>7638000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>7561000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>7240000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8841000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>6795000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>6746000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>6327000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>8451000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>7320000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>7245000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1145,115 +1157,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2654000</v>
+      </c>
+      <c r="E12" s="3">
         <v>2429000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2471000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2306000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2226000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2248000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2226000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2216000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2226000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2146000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2158000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2093000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1965000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1816000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1754000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1684000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1715000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1928000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1601000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1589000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1479000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1500000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1531000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1557000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1562000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1426000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1475000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1564000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1543000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1496000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1473000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1572000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1608000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>1521000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>1510000</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1359,222 +1375,231 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E14" s="3">
         <v>123000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>192000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>139000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>79000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>193000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>180000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>263000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>234000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>217000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>199000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>185000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>108000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>39000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>4699000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>59000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>125000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>79000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>172000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>193000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>81000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>67000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>54000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>103000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>183000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>39000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>161000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>104000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>102000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>94000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>309000</v>
-      </c>
-      <c r="AH14" s="3">
-        <v>136000</v>
       </c>
       <c r="AI14" s="3">
         <v>136000</v>
       </c>
       <c r="AJ14" s="3">
+        <v>136000</v>
+      </c>
+      <c r="AK14" s="3">
         <v>191000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>544000</v>
+      </c>
+      <c r="E15" s="3">
         <v>548000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>591000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>624000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>743000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>749000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>755000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>763000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>870000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>886000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>907000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>919000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>268000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>279000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>299000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>303000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>342000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>347000</v>
-      </c>
-      <c r="U15" s="3">
-        <v>345000</v>
       </c>
       <c r="V15" s="3">
         <v>345000</v>
       </c>
       <c r="W15" s="3">
+        <v>345000</v>
+      </c>
+      <c r="X15" s="3">
         <v>365000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>400000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>407000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>414000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>424000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>407000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>424000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>434000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>415000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>394000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>400000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>411000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>441000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>397000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>302000</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1609,222 +1634,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>10737000</v>
+      </c>
+      <c r="E17" s="3">
         <v>9708000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9755000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9246000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9535000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9431000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9218000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9012000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9540000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9043000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9204000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8822000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7338000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6691000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11184000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6301000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6686000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6207000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6217000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6156000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6131000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6268000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6431000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6341000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6880000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6215000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6461000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6415000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>6853000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6361000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6550000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6355000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>6819000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>6246000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>5998000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>5166000</v>
+      </c>
+      <c r="E18" s="3">
         <v>4422000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4304000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4061000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4752000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3849000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3723000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3441000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4296000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3355000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3071000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2623000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4502000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3822000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-824000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3427000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4541000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3878000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3583000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3211000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4308000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3528000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3183000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2877000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4257000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3399000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3101000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2778000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>4161000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3315000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3039000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2749000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>4074000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2959000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>3037000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1862,543 +1894,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E20" s="3">
         <v>94000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>44000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>84000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>26000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>68000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>67000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>103000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>102000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-71000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-180000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-174000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-315000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>7000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-41000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>312000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-17000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-11000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-33000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>4000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>92000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>99000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>134000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>198000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>192000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>291000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>294000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>409000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>262000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>220000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>168000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>189000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>99000</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>5613000</v>
+      </c>
+      <c r="E21" s="3">
         <v>4876000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4890000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4641000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5411000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4572000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4410000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4137000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5063000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4139000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4498000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3909000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5159000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4282000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-58000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4143000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5605000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4593000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4303000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3910000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4997000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4280000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>4023000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3726000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>5145000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4338000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>3997000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>3789000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>5157000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>4423000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3989000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3665000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>4961000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>3804000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>3679000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>978000</v>
+      </c>
+      <c r="E22" s="3">
         <v>892000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>866000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>842000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>878000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>876000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>888000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>872000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>955000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>908000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>856000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>787000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>704000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>667000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>679000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>705000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>697000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>585000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>600000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>614000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>579000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>456000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>465000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>494000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>525000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>509000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>519000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>529000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>548000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>533000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>475000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>469000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>481000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>450000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>451000</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>4152000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3448000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3390000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3169000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3782000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2865000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2720000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2375000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3109000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2218000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2144000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1656000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3624000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2840000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1496000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2681000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4156000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3276000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2972000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2595000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3696000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3076000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2810000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2482000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3866000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3088000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2774000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2540000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3907000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3191000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2826000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2500000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>3761000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2698000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2685000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>725000</v>
+      </c>
+      <c r="E24" s="3">
         <v>512000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>239000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>240000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>638000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>464000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>217000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-45000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-210000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>322000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>403000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>108000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>435000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>521000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-249000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>224000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>124000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1745000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>530000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>344000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>580000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>505000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>499000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>345000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>126000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>579000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>441000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>428000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>632000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>367000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>612000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>356000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>529000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>459000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>653000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2504,222 +2552,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>3427000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2936000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3151000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2929000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3144000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2401000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2503000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2420000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3319000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1896000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1741000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1548000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3189000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2319000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1247000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2457000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4032000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5021000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2442000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2251000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3116000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2571000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2311000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2137000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3740000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2509000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2333000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2112000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3275000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2824000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2214000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2144000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>3232000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2239000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2032000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>3427000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2936000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3151000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2929000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3144000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2401000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2503000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2420000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3319000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1896000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1741000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1548000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3189000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2319000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1247000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2457000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4032000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5021000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2442000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2251000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3116000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2571000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2311000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2137000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3740000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2509000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2333000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2112000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3275000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2824000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2214000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2144000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>3232000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2239000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>2032000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2825,8 +2882,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2884,12 +2944,12 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
       <c r="X29" s="3">
         <v>0</v>
       </c>
@@ -2903,28 +2963,28 @@
         <v>0</v>
       </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>236000</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>153000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>1000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-6871000</v>
       </c>
-      <c r="AG29" s="3" t="s">
+      <c r="AH29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI29" s="3" t="s">
-        <v>24</v>
+      <c r="AI29" s="3">
+        <v>0</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>24</v>
@@ -2932,8 +2992,11 @@
       <c r="AK29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3039,8 +3102,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3146,222 +3212,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-97000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-94000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-44000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-84000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-26000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-68000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-67000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-103000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-102000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>71000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>180000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>174000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>315000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-7000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>41000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-312000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>17000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>11000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>33000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-92000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-99000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-134000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-198000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-192000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-291000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-294000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-409000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-262000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-220000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-168000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-189000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-99000</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3427000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2936000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3151000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2929000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3144000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2401000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2503000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2420000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3319000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1896000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1741000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1548000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3189000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2319000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1247000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2457000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4032000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5021000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2442000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2251000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3116000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2571000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2311000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2137000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3740000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2745000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2333000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2265000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3276000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-4047000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2214000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2144000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>3232000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2239000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>2032000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3467,227 +3542,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3427000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2936000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3151000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2929000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3144000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2401000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2503000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2420000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3319000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1896000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1741000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1548000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3189000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2319000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1247000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2457000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4032000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5021000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2442000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2251000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3116000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2571000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2311000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2137000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3740000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2745000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2333000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2265000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3276000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-4047000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2214000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2144000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>3232000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2239000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>2032000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45808</v>
+      </c>
+      <c r="E38" s="2">
         <v>45716</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45626</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45535</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45443</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45351</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45260</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45169</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45077</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44985</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44895</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44804</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44712</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44620</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44530</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44439</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44347</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44255</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44165</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44074</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43982</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43890</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43799</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43708</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43616</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43524</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43434</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43343</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43251</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43159</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43069</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42978</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42886</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42794</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42704</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3725,8 +3809,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3764,115 +3849,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10786000</v>
+      </c>
+      <c r="E41" s="3">
         <v>17406000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10941000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10616000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10454000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9481000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8244000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11613000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9765000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8219000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6813000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10448000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>21383000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>22682000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>17938000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>23059000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>30098000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>22321000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>28001000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>27276000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>37239000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>23829000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>24540000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>31083000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>20514000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>14720000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>10824000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>18455000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>21620000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>19487000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>21310000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>21321000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>21784000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>19748000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>18592000</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3880,218 +3969,224 @@
         <v>417000</v>
       </c>
       <c r="E42" s="3">
+        <v>417000</v>
+      </c>
+      <c r="F42" s="3">
         <v>370000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>295000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>207000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>423000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>446000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>470000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>422000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>550000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>537000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>772000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>519000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>707000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>4900000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>16251000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>16456000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>13543000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>10592000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>15003000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>5818000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2029000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2904000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>4621000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>17313000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>25310000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>38567000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>41639000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>45641000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>50968000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>50270000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>45576000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>44294000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>39604000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>39614000</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9413000</v>
+      </c>
+      <c r="E43" s="3">
         <v>8051000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8177000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8021000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8695000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7297000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6804000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6519000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7713000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6213000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6197000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5937000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5953000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4588000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4462000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4482000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5409000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4637000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4423000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4576000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6329000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4162000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4050000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3820000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5910000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3993000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3975000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3729000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5938000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3902000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3798000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3591000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>5300000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3721000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3690000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>24</v>
+      <c r="D44" s="3">
+        <v>303000</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>24</v>
@@ -4099,11 +4194,11 @@
       <c r="F44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H44" s="3">
         <v>334000</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>24</v>
@@ -4111,15 +4206,15 @@
       <c r="J44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" s="3">
         <v>298000</v>
       </c>
-      <c r="L44" s="3" t="s">
+      <c r="M44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
       <c r="N44" s="3">
         <v>0</v>
       </c>
@@ -4138,8 +4233,8 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>24</v>
+      <c r="T44" s="3">
+        <v>0</v>
       </c>
       <c r="U44" s="3" t="s">
         <v>24</v>
@@ -4147,11 +4242,11 @@
       <c r="V44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="W44" s="3">
+      <c r="W44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="X44" s="3">
         <v>211000</v>
-      </c>
-      <c r="X44" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Y44" s="3" t="s">
         <v>24</v>
@@ -4159,11 +4254,11 @@
       <c r="Z44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AA44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB44" s="3">
         <v>320000</v>
-      </c>
-      <c r="AB44" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AC44" s="3" t="s">
         <v>24</v>
@@ -4171,29 +4266,32 @@
       <c r="AD44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AE44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF44" s="3">
         <v>398000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>496000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>436000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>312000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>300000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>391000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4224,223 +4322,229 @@
       <c r="L45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N45" s="3">
         <v>4014000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3847000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3778000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3698000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3778000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3325000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3604000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3243000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3235000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3084000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2543000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3422000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3046000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2860000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2329000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3594000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3572000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3186000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>5986000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2879000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2731000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2535000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2837000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2547000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>2511000</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>24579000</v>
+      </c>
+      <c r="E46" s="3">
         <v>30116000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>23503000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>23072000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>22554000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>21063000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>19289000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>22166000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>21004000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>18696000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>17561000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>21004000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>31633000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>31675000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>31078000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>47117000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>55567000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>43744000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>46251000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>49939000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>52140000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>33442000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>34540000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>42384000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>46386000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>47617000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>56938000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>67009000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>76159000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>77732000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>78545000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>73335000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>74515000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>66011000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>64734000</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2100000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2000000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1900000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2300000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2000000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1900000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1800000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1700000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1600000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2100000</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -4513,222 +4617,231 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>56667000</v>
+      </c>
+      <c r="E48" s="3">
         <v>43670000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>26432000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>23094000</v>
       </c>
-      <c r="G48" s="3">
-        <v>28836000</v>
-      </c>
       <c r="H48" s="3">
+        <v>28826000</v>
+      </c>
+      <c r="I48" s="3">
         <v>19117000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>18009000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>17644000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>17069000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>16345000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14351000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12280000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9716000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8609000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8029000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7610000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7049000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6816000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6627000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6401000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>9044000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>8048000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>8170000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>8264000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6252000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6197000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6003000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5918000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5897000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>5904000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>5868000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>5586000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>5315000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>5070000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>4882000</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>66794000</v>
+      </c>
+      <c r="E49" s="3">
         <v>67302000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>67883000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>68519000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>69120000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>69851000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>70609000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>71280000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>72098000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>72206000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>73106000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>74128000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>45251000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>45521000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>45723000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>46043000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>46365000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>46708000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>46938000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>47272000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>47507000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>47869000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>48302000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>48594000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>49058000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>49454000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>49881000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>49997000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>50425000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>49365000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>49758000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>50206000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>50724000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>50292000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>50051000</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4834,8 +4947,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4941,115 +5057,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6344000</v>
+      </c>
+      <c r="E52" s="3">
         <v>6491000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>16781000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>15010000</v>
       </c>
-      <c r="G52" s="3">
-        <v>6193000</v>
-      </c>
       <c r="H52" s="3">
+        <v>6203000</v>
+      </c>
+      <c r="I52" s="3">
         <v>12463000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11859000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11629000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10387000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10120000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>23451000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>22897000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>22697000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>22839000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>22067000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>22154000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>22126000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>20841000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>10198000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>9934000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6747000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7345000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7431000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6987000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7013000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6170000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5496000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5434000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5370000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5200000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>4591000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>4470000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>4437000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>4009000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>3933000</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5155,115 +5277,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>168361000</v>
+      </c>
+      <c r="E54" s="3">
         <v>161378000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>148483000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>144214000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>140976000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>137082000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>134324000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>136662000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>134384000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>131620000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>128469000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>130309000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>109297000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>108644000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>106897000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>122924000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>131107000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>118109000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>110014000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>113546000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>115438000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>96704000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>98443000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>106229000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>108709000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>109438000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>118318000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>128358000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>137851000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>138201000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>138762000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>133597000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>134991000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>125382000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>123600000</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5301,8 +5429,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5340,650 +5469,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5113000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2423000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2679000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2207000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2357000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1658000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1107000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1034000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1204000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1610000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1647000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1461000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1317000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1124000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1034000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>749000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>745000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>812000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>724000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>534000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>637000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>533000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>534000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>486000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>580000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>603000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>587000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>527000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>529000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>603000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>554000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>593000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>599000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>481000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>615000</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9451000</v>
+      </c>
+      <c r="E58" s="3">
         <v>8167000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8162000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>9201000</v>
       </c>
-      <c r="G58" s="3">
-        <v>11905000</v>
-      </c>
       <c r="H58" s="3">
+        <v>11895000</v>
+      </c>
+      <c r="I58" s="3">
         <v>5510000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6321000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4499000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4061000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5415000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>9746000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>16097000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3749000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6248000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4998000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>6748000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>8250000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5758000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>7251000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2997000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2371000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2355000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>999000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3748000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4494000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>4487000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>6477000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3743000</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>4491000</v>
       </c>
       <c r="AF58" s="3">
         <v>4491000</v>
       </c>
       <c r="AG58" s="3">
+        <v>4491000</v>
+      </c>
+      <c r="AH58" s="3">
         <v>2499000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>4998000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>9797000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3498000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>3838000</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15836000</v>
+      </c>
+      <c r="E59" s="3">
         <v>17194000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>16558000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>18865000</v>
       </c>
-      <c r="G59" s="3">
-        <v>15366000</v>
-      </c>
       <c r="H59" s="3">
+        <v>15376000</v>
+      </c>
+      <c r="I59" s="3">
         <v>15921000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15273000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>18006000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15772000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14119000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15713000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17261000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14445000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13461000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12849000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>15574000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>15169000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>13680000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>13372000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>15217000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>14192000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>12852000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>13059000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>14641000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>13556000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>12896000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>13251000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>15292000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>14104000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>12874000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>12441000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>14635000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>13782000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>11811000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>11894000</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>32643000</v>
+      </c>
+      <c r="E60" s="3">
         <v>29623000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>29052000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>32045000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>31544000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>24885000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>24407000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>25357000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>23090000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>22880000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>27106000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>34819000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>19511000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>20833000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>18881000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>23071000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>24164000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>20250000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>21347000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>18748000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>17200000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>15740000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>14592000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>18875000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>18630000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>17986000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>20315000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>19562000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>19124000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>17968000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>15494000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>20226000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>24178000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>15790000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>16347000</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>99501000</v>
+      </c>
+      <c r="E61" s="3">
         <v>101009000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>91382000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>84991000</v>
       </c>
-      <c r="G61" s="3">
-        <v>82509000</v>
-      </c>
       <c r="H61" s="3">
+        <v>82519000</v>
+      </c>
+      <c r="I61" s="3">
         <v>82470000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>82468000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>84442000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>86420000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>86396000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>81173000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>75480000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>72110000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>72165000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>73433000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>75970000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>75995000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>63541000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>63531000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>67769000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>69209000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>49299000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>50643000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>50684000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>51656000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>51672000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>51561000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>54386000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>56128000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>55145000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>57119000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>47355000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>47132000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>49518000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>51427000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13902000</v>
+      </c>
+      <c r="E62" s="3">
         <v>9928000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9553000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>11038000</v>
       </c>
-      <c r="G62" s="3">
-        <v>12759000</v>
-      </c>
       <c r="H62" s="3">
+        <v>16441000</v>
+      </c>
+      <c r="I62" s="3">
         <v>17797000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>16576000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>17595000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16578000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16652000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>23966000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>25459000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>23444000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>23857000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>24241000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>25013000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>24996000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>24681000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>16520000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>16889000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>16312000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>16784000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>17023000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>17651000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>16060000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>15542000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>15387000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>15846000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>15726000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>16816000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>9849000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>9650000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>9435000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>9051000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>6981000</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6089,8 +6237,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6196,8 +6347,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6303,115 +6457,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>147392000</v>
+      </c>
+      <c r="E66" s="3">
         <v>144117000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>134247000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>132945000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>131737000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>130900000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>129946000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>133821000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>132828000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>133532000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>132715000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>136184000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>115517000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>117340000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>116998000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>124465000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>125869000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>109209000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>102097000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>104055000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>103364000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>82469000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>82880000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>87796000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>86924000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>85724000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>87746000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>90291000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>91479000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>90412000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>82894000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>77638000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>81131000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>74767000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>75138000</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6449,8 +6609,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6556,8 +6717,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6663,8 +6827,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6770,8 +6937,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6877,115 +7047,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-15481000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-17368000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-19045000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-20939000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-22628000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-24533000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-25431000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-26428000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-27620000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-29721000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-30617000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-31134000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-31336000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-33147000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-34076000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-25679000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-20120000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-16206000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-17095000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-15410000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-12696000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-10771000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-9174000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-6446000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-3496000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-1284000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5107000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>12022000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>19111000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>20037000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>28296000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>28586000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>27598000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>25576000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>24375000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7091,8 +7267,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7198,8 +7377,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7305,115 +7487,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20451000</v>
+      </c>
+      <c r="E76" s="3">
         <v>16730000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13746000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10816000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8704000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5623000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3866000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2370000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1073000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-2421000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-4246000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-5875000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-6220000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-8696000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-10101000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-1541000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5238000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8900000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7917000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9491000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12074000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14235000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>15563000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>18433000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>21785000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>23714000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>30572000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>38067000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>46372000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>47789000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>55868000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>55959000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>53860000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>50615000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>48462000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7519,227 +7707,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45808</v>
+      </c>
+      <c r="E80" s="2">
         <v>45716</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45626</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45535</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45443</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45351</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45260</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45169</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45077</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44985</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44895</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44804</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44712</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44620</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44530</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44439</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44347</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44255</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44165</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44074</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43982</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43890</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43799</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43708</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43616</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43524</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43434</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43343</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43251</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43159</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43069</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42978</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42886</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42794</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42704</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3427000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2936000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3151000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2929000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3144000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2401000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2503000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2420000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3319000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1896000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1741000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1548000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3189000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2319000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1247000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2457000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4032000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5021000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2442000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2251000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3116000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2571000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2311000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2137000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3740000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2745000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2333000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2265000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3276000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-4047000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2214000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2144000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>3232000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2239000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>2032000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7777,115 +7974,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>811000</v>
+      </c>
+      <c r="E83" s="3">
         <v>808000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>798000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>712000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>716000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>672000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>591000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>547000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>563000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>496000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1498000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1466000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>831000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>775000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>759000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>757000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>752000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>732000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>731000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>701000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>722000</v>
-      </c>
-      <c r="X83" s="3">
-        <v>748000</v>
       </c>
       <c r="Y83" s="3">
         <v>748000</v>
       </c>
       <c r="Z83" s="3">
+        <v>748000</v>
+      </c>
+      <c r="AA83" s="3">
         <v>750000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>754000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>741000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>704000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>720000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>702000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>699000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>688000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>696000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>719000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>656000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>543000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7991,8 +8192,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8098,8 +8302,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8205,8 +8412,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8312,8 +8522,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8419,115 +8632,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6157000</v>
+      </c>
+      <c r="E89" s="3">
         <v>5933000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1304000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7427000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6081000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5475000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>143000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6974000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5647000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4275000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>849000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6394000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3985000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3845000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3682000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5391000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4842000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3704000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1388000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>5953000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3614000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3012000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>513000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>6000000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>4422000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2861000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>546000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>6722000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>4660000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3310000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>850000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>6566000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>4466000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>2699000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1086000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8565,115 +8784,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9080000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5862000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3970000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2303000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2798000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1674000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1080000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1314000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1913000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2628000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2435000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1719000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1423000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1101000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-925000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1062000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-717000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-414000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-568000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-436000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-433000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-396000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-349000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-386000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-413000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-443000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-421000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-383000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-378000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-286000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-599000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-473000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-525000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-440000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-757000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8779,8 +9002,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8886,115 +9112,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-9182000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5976000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3788000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2765000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2766000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1783000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1249000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1562000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1612000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2778000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2658000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-29436000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1161000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>2432000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>10730000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-781000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3911000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3384000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>3852000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-9655000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4256000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>480000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>1233000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>12386000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>7906000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>13199000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>1920000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>3532000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>3160000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1257000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-5710000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1818000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-5846000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-728000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-9717000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9032,115 +9264,119 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1403000</v>
+      </c>
+      <c r="E96" s="3">
         <v>1119000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1118000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1103000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1102000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>1099000</v>
       </c>
       <c r="I96" s="3">
         <v>1099000</v>
       </c>
       <c r="J96" s="3">
+        <v>1099000</v>
+      </c>
+      <c r="K96" s="3">
         <v>1091000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1082000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>863000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-863000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-860000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-854000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-855000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-861000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-887000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-917000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-699000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-717000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-730000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-740000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-768000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-767000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-795000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-806000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-670000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-714000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-742000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-778000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-783000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-791000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-788000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-787000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-612000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-614000</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9246,8 +9482,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9353,8 +9592,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9460,325 +9702,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3814000</v>
+      </c>
+      <c r="E100" s="3">
         <v>6559000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2938000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4585000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2274000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2463000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2289000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3528000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2440000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-105000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1855000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>12310000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4026000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1579000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-12053000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-11468000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>6798000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-6129000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-4554000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-6493000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>14133000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-4169000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-8294000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-7802000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-6461000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-12239000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-10023000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-13333000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-5459000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-4020000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>4938000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-5441000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>3287000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-940000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-973000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-68000</v>
+      </c>
+      <c r="E101" s="3">
         <v>8000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>26000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-36000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-49000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>14000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>29000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-203000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-97000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>46000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>29000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-203000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-97000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>46000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-116000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-181000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>48000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>129000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>39000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>232000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-81000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-34000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>5000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-15000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-73000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>75000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-74000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-86000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-228000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>144000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-89000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>230000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>129000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>125000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-418000</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6620000</v>
+      </c>
+      <c r="E102" s="3">
         <v>6465000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>325000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>162000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>973000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1237000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3369000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1848000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1546000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1406000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3635000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-10935000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1299000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4744000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-5121000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-7039000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>7777000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-5680000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>725000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-9963000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>13410000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-711000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-6543000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>10569000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>5794000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>3896000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-7631000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-3165000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>2133000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1823000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-11000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-463000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>2036000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1156000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-10022000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ORCL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ORCL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
   <si>
     <t>ORCL</t>
   </si>
@@ -656,482 +656,506 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="25" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="39" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="27" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="41" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45991</v>
+      </c>
+      <c r="F7" s="2">
         <v>45900</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45808</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45716</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45626</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45535</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45443</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45351</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45260</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45169</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45077</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44985</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44895</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44804</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44712</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44620</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44530</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44439</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44347</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44255</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44165</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44074</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43982</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43890</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43799</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43708</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43616</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43524</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43434</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43343</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43251</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43159</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43069</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42978</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42886</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42794</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42704</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>17190000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>16058000</v>
+      </c>
+      <c r="F8" s="3">
         <v>14926000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>15903000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>14130000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>14059000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>13307000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>14287000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>13280000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>12941000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>12453000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>13836000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>12398000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>12275000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>11445000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>11840000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>10513000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>10360000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>9728000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>11227000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>10085000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>9800000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>9367000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>10439000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>9796000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>9614000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>9218000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>11137000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>9614000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>9562000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>9193000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>11014000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>9676000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>9589000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>9104000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>10893000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>9205000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>9035000</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6092000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>5374000</v>
+      </c>
+      <c r="F9" s="3">
         <v>4884000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>4741000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>4195000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>4085000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>3906000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>3924000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>3869000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>3740000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>3610000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>3730000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>3439000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>3358000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>3037000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>2397000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>2218000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>2159000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>2103000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>2122000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1915000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>1939000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1880000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>1969000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>1964000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>2048000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>1957000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>2063000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>1976000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>2001000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>1953000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>2173000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>2881000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>2843000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>2777000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>2442000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>1885000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>1790000</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>11098000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>10684000</v>
+      </c>
+      <c r="F10" s="3">
         <v>10042000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>11162000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>9935000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>9974000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>9401000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>10363000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>9411000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>9201000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>8843000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>10106000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>8959000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>8917000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>8408000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>9443000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>8295000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>8201000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>7625000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>9105000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>8170000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>7861000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>7487000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>8470000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>7832000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>7566000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>7261000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>9074000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>7638000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>7561000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>7240000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>8841000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>6795000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>6746000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>6327000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>8451000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>7320000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>7245000</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1171,121 +1195,129 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2607000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2561000</v>
+      </c>
+      <c r="F12" s="3">
         <v>2491000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>2654000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>2429000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>2471000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>2306000</v>
-      </c>
-      <c r="I12" s="3">
-        <v>2226000</v>
-      </c>
-      <c r="J12" s="3">
-        <v>2248000</v>
       </c>
       <c r="K12" s="3">
         <v>2226000</v>
       </c>
       <c r="L12" s="3">
-        <v>2216000</v>
+        <v>2248000</v>
       </c>
       <c r="M12" s="3">
         <v>2226000</v>
       </c>
       <c r="N12" s="3">
+        <v>2216000</v>
+      </c>
+      <c r="O12" s="3">
+        <v>2226000</v>
+      </c>
+      <c r="P12" s="3">
         <v>2146000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>2158000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>2093000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>1965000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>1816000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>1754000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>1684000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>1715000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>1928000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>1601000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>1589000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>1479000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>1500000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>1531000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>1557000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>1562000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>1426000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>1475000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>1564000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>1543000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>1496000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>1473000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>1572000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AM12" s="3">
         <v>1608000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AN12" s="3">
         <v>1521000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AO12" s="3">
         <v>1510000</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1397,234 +1429,252 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-2086000</v>
+      </c>
+      <c r="F14" s="3">
         <v>459000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>99000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>123000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>192000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>139000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>79000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>193000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>180000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>263000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>234000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>217000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>199000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>185000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>108000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>39000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>4699000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>59000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>125000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>79000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>172000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>193000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>81000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>67000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>54000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>103000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>183000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>39000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>161000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>104000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AI14" s="3">
         <v>102000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AJ14" s="3">
         <v>94000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AK14" s="3">
         <v>309000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AL14" s="3">
         <v>136000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AM14" s="3">
         <v>136000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AN14" s="3">
         <v>191000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AO14" s="3">
         <v>126000</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>413000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>407000</v>
+      </c>
+      <c r="F15" s="3">
         <v>420000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>544000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>548000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>591000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>624000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>743000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>749000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>755000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>763000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>870000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>886000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>907000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>919000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>268000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>279000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>299000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>303000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>342000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>347000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>345000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>345000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>365000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>400000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>407000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>414000</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>424000</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>407000</v>
       </c>
       <c r="AE15" s="3">
         <v>424000</v>
       </c>
       <c r="AF15" s="3">
+        <v>407000</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>424000</v>
+      </c>
+      <c r="AH15" s="3">
         <v>434000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AI15" s="3">
         <v>415000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AJ15" s="3">
         <v>394000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AK15" s="3">
         <v>400000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AL15" s="3">
         <v>411000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AM15" s="3">
         <v>441000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AN15" s="3">
         <v>397000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AO15" s="3">
         <v>302000</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1661,234 +1711,248 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>11573000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>10920000</v>
+      </c>
+      <c r="F17" s="3">
         <v>10242000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>10737000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>9708000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>9755000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>9246000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>9535000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>9431000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>9218000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>9012000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>9540000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>9043000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>9204000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>8822000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>7338000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>6691000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>11184000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>6301000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>6686000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>6207000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>6217000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>6156000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>6131000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>6268000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>6431000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>6341000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>6880000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>6215000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>6461000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>6415000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>6853000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>6361000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>6550000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>6355000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>6819000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>6246000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>5998000</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>5617000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>5138000</v>
+      </c>
+      <c r="F18" s="3">
         <v>4684000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>5166000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>4422000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>4304000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>4061000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>4752000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>3849000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>3723000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>3441000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>4296000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>3355000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>3071000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>2623000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>4502000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>3822000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-824000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>3427000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>4541000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>3878000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>3583000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>3211000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>4308000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>3528000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>3183000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>2877000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>4257000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>3399000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>3101000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>2778000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>4161000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>3315000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>3039000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>2749000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>4074000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>2959000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>3037000</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1928,573 +1992,605 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>17000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-22000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>97000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>94000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>5000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>44000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>84000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>26000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>68000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>67000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>103000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>102000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-71000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-180000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-174000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-315000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>7000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-41000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>312000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-17000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-11000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-33000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>4000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>92000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>99000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>134000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>198000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>192000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>291000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>294000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>409000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>262000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>220000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>168000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>189000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>99000</v>
       </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>5973000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>5528000</v>
+      </c>
+      <c r="F21" s="3">
         <v>5126000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>5613000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>4876000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>4890000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>4641000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>5411000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>4572000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>4410000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>4137000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>5063000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>4139000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>4498000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>3909000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>5159000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>4282000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-58000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>4143000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>5605000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>4593000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>4303000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>3910000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>4997000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>4280000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>4023000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>3726000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>5145000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>4338000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>3997000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>3789000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>5157000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>4423000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>3989000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>3665000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>4961000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>3804000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>3679000</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>1180000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1057000</v>
+      </c>
+      <c r="F22" s="3">
         <v>923000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>978000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>892000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>866000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>842000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>878000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>876000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>888000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>872000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>955000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>908000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>856000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>787000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>704000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>667000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>679000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>705000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>697000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>585000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>600000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>614000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>579000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>456000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>465000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>494000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>525000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>509000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>519000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>529000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>548000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>533000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>475000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>469000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>481000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AN22" s="3">
         <v>450000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AO22" s="3">
         <v>451000</v>
       </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>4416000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>6342000</v>
+      </c>
+      <c r="F23" s="3">
         <v>3427000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>4152000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>3448000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>3390000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>3169000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>3782000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>2865000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>2720000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>2375000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>3109000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>2218000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>2144000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>1656000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>3624000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>2840000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-1496000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>2681000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>4156000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>3276000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>2972000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>2595000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>3696000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>3076000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>2810000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>2482000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>3866000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>3088000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>2774000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>2540000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>3907000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>3191000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>2826000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>2500000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>3761000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>2698000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>2685000</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>695000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>207000</v>
+      </c>
+      <c r="F24" s="3">
         <v>500000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>725000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>512000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>239000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>240000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>638000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>464000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>217000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-45000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-210000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>322000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>403000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>108000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>435000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>521000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-249000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>224000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>124000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-1745000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>530000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>344000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>580000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>505000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>499000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>345000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>126000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>579000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>441000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>428000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>632000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>367000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>612000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>356000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>529000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>459000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>653000</v>
       </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2606,234 +2702,252 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>3721000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>6135000</v>
+      </c>
+      <c r="F26" s="3">
         <v>2927000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>3427000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>2936000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>3151000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>2929000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>3144000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>2401000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>2503000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>2420000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>3319000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>1896000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>1741000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1548000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>3189000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>2319000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-1247000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>2457000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>4032000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>5021000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>2442000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>2251000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>3116000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>2571000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>2311000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>2137000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>3740000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>2509000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>2333000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>2112000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>3275000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>2824000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>2214000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>2144000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>3232000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>2239000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>2032000</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>3699000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>6135000</v>
+      </c>
+      <c r="F27" s="3">
         <v>2927000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>3427000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>2936000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>3151000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>2929000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>3144000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>2401000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>2503000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>2420000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>3319000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>1896000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>1741000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>1548000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>3189000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>2319000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-1247000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>2457000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>4032000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>5021000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>2442000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>2251000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>3116000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>2571000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>2311000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>2137000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>3740000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>2509000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>2333000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>2112000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>3275000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>2824000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>2214000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>2144000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>3232000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>2239000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>2032000</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2945,8 +3059,14 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3010,15 +3130,15 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
       <c r="AA29" s="3">
         <v>0</v>
       </c>
@@ -3029,37 +3149,43 @@
         <v>0</v>
       </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>236000</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>153000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AI29" s="3">
         <v>1000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AJ29" s="3">
         <v>-6871000</v>
-      </c>
-      <c r="AI29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AJ29" s="3">
-        <v>0</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>24</v>
+      <c r="AL29" s="3">
+        <v>0</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AN29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AO29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3171,8 +3297,14 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3284,234 +3416,252 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-57000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="F32" s="3">
         <v>22000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-97000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-94000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-5000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-44000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-84000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-26000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-68000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-67000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-103000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-102000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>71000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>180000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>174000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>315000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-7000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>41000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-312000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>17000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>11000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>2000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>33000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-92000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-99000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-134000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-198000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-192000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-291000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-294000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-409000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-262000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-220000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-168000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>-189000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>-99000</v>
       </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3721000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>6135000</v>
+      </c>
+      <c r="F33" s="3">
         <v>2927000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>3427000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>2936000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>3151000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>2929000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>3144000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>2401000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>2503000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>2420000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>3319000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>1896000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>1741000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>1548000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>3189000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>2319000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-1247000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>2457000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>4032000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>5021000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>2442000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>2251000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>3116000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>2571000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>2311000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>2137000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>3740000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>2745000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>2333000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>2265000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>3276000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-4047000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>2214000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>2144000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>3232000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>2239000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>2032000</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3623,239 +3773,257 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3721000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>6135000</v>
+      </c>
+      <c r="F35" s="3">
         <v>2927000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>3427000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>2936000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>3151000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>2929000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>3144000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>2401000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>2503000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>2420000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>3319000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>1896000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>1741000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>1548000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>3189000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>2319000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-1247000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>2457000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>4032000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>5021000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>2442000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>2251000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>3116000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>2571000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>2311000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>2137000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>3740000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>2745000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>2333000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>2265000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>3276000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-4047000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>2214000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>2144000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>3232000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>2239000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>2032000</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45991</v>
+      </c>
+      <c r="F38" s="2">
         <v>45900</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45808</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45716</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45626</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45535</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45443</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45351</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45260</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45169</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45077</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44985</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44895</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44804</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44712</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44620</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44530</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44439</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44347</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44255</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44165</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44074</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43982</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43890</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43799</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43708</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43616</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43524</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43434</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43343</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43251</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43159</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43069</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42978</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42886</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42794</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42704</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3895,8 +4063,10 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3936,388 +4106,408 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>38455000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>19241000</v>
+      </c>
+      <c r="F41" s="3">
         <v>10445000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>10786000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>17406000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>10941000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>10616000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>10454000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>9481000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>8244000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>11613000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>9765000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>8219000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>6813000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>10448000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>21383000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>22682000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>17938000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>23059000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>30098000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>22321000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>28001000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>27276000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>37239000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>23829000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>24540000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>31083000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>20514000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>14720000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>10824000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>18455000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>21620000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>19487000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>21310000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>21321000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>21784000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>19748000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>18592000</v>
       </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>677000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>525000</v>
+      </c>
+      <c r="F42" s="3">
         <v>560000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>417000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>417000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>370000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>295000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>207000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>423000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>446000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>470000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>422000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>550000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>537000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>772000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>519000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>707000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>4900000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>16251000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>16456000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>13543000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>10592000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>15003000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>5818000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>2029000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>2904000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>4621000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>17313000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>25310000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>38567000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>41639000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>45641000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AJ42" s="3">
         <v>50968000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AK42" s="3">
         <v>50270000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AL42" s="3">
         <v>45576000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AM42" s="3">
         <v>44294000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AN42" s="3">
         <v>39604000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AO42" s="3">
         <v>39614000</v>
       </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10719000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>9440000</v>
+      </c>
+      <c r="F43" s="3">
         <v>8843000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>9413000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>8051000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>8177000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>8021000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>8695000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>7297000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>6804000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>6519000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>7713000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>6213000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>6197000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>5937000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>5953000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>4588000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>4462000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>4482000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>5409000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>4637000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>4423000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>4576000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>6329000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>4162000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>4050000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>3820000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>5910000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>3993000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>3975000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>3729000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>5938000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>3902000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>3798000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>3591000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>5300000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>3721000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>3690000</v>
       </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E44" s="3">
-        <v>303000</v>
+      <c r="E44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>24</v>
+      <c r="G44" s="3">
+        <v>303000</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I44" s="3">
-        <v>334000</v>
+      <c r="I44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>24</v>
+      <c r="K44" s="3">
+        <v>334000</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M44" s="3">
-        <v>298000</v>
+      <c r="M44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>24</v>
       </c>
       <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+        <v>298000</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4334,62 +4524,68 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="W44" s="3" t="s">
-        <v>24</v>
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+      <c r="W44" s="3">
+        <v>0</v>
       </c>
       <c r="X44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y44" s="3">
-        <v>211000</v>
+      <c r="Y44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>24</v>
+      <c r="AA44" s="3">
+        <v>211000</v>
       </c>
       <c r="AB44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC44" s="3">
-        <v>320000</v>
+      <c r="AC44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AD44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>24</v>
+      <c r="AE44" s="3">
+        <v>320000</v>
       </c>
       <c r="AF44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AG44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI44" s="3">
         <v>398000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>496000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>436000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>312000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>300000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>391000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4426,238 +4622,250 @@
       <c r="N45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q45" s="3">
         <v>4014000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>3847000</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>3778000</v>
-      </c>
-      <c r="R45" s="3">
-        <v>3698000</v>
       </c>
       <c r="S45" s="3">
         <v>3778000</v>
       </c>
       <c r="T45" s="3">
+        <v>3698000</v>
+      </c>
+      <c r="U45" s="3">
+        <v>3778000</v>
+      </c>
+      <c r="V45" s="3">
         <v>3325000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>3604000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>3243000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>3235000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>3084000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>2543000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>3422000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>3046000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>2860000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>2329000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>3594000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>3572000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>3186000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>5986000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>2879000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>2731000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>2535000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>2837000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>2547000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>2511000</v>
       </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>54874000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>34366000</v>
+      </c>
+      <c r="F46" s="3">
         <v>24634000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>24579000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>30116000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>23503000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>23072000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>22554000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>21063000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>19289000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>22166000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>21004000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>18696000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>17561000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>21004000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>31633000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>31675000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>31078000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>47117000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>55567000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>43744000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>46251000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>49939000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>52140000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>33442000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>34540000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>42384000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>46386000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>47617000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>56938000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>67009000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>76159000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>77732000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>78545000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>73335000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>74515000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>66011000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>64734000</v>
       </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2200000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>416000</v>
+      </c>
+      <c r="F47" s="3">
         <v>2100000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>2100000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>2000000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>1900000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>2300000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>2000000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>1900000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>1800000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>1700000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>1600000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>2100000</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
@@ -4727,234 +4935,252 @@
       <c r="AM47" s="3">
         <v>0</v>
       </c>
+      <c r="AN47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>83617000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>67875000</v>
+      </c>
+      <c r="F48" s="3">
         <v>53194000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>56667000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>43670000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>26432000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>23094000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>28826000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>19117000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>18009000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>17644000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>17069000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>16345000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>14351000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>12280000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>9716000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>8609000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>8029000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>7610000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>7049000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>6816000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>6627000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>6401000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>9044000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>8048000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>8170000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>8264000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>6252000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>6197000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>6003000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>5918000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>5897000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>5904000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>5868000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>5586000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>5315000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>5070000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>4882000</v>
       </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>65915000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>65967000</v>
+      </c>
+      <c r="F49" s="3">
         <v>66378000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>66794000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>67302000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>67883000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>68519000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>69120000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>69851000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>70609000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>71280000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>72098000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>72206000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>73106000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>74128000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>45251000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>45521000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>45723000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>46043000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>46365000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>46708000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>46938000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>47272000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>47507000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>47869000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>48302000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>48594000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>49058000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>49454000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>49881000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>49997000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>50425000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>49365000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>49758000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>50206000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>50724000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>50292000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>50051000</v>
       </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5066,8 +5292,14 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5179,121 +5411,133 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>27274000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>24829000</v>
+      </c>
+      <c r="F52" s="3">
         <v>22409000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>6344000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>6491000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>16781000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>15010000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>6203000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>12463000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>11859000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>11629000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>10387000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>10120000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>23451000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>22897000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>22697000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>22839000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>22067000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>22154000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>22126000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>20841000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>10198000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>9934000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>6747000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>7345000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>7431000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>6987000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>7013000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>6170000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>5496000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>5434000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>5370000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>5200000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>4591000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>4470000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>4437000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>4009000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>3933000</v>
       </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5405,121 +5649,133 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>245240000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>204984000</v>
+      </c>
+      <c r="F54" s="3">
         <v>180449000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>168361000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>161378000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>148483000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>144214000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>140976000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>137082000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>134324000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>136662000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>134384000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>131620000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>128469000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>130309000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>109297000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>108644000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>106897000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>122924000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>131107000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>118109000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>110014000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>113546000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>115438000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>96704000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>98443000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>106229000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>108709000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>109438000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>118318000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>128358000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>137851000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>138201000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>138762000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>133597000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>134991000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>125382000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>123600000</v>
       </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5559,8 +5815,10 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5600,686 +5858,724 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9474000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>10140000</v>
+      </c>
+      <c r="F57" s="3">
         <v>8203000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>5113000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2423000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2679000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2207000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2357000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1658000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1107000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1034000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1204000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1610000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1647000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1461000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1317000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1124000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1034000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>749000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>745000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>812000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>724000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>534000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>637000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>533000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>534000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>486000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>580000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>603000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>587000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>527000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>529000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>603000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>554000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>593000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>599000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>481000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>615000</v>
       </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>13224000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>10859000</v>
+      </c>
+      <c r="F58" s="3">
         <v>11612000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>9442000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>8167000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>8162000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>9201000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>11895000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>5510000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>6321000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>4499000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>4061000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>5415000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>9746000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>16097000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>3749000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>6248000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>4998000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>6748000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>8250000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>5758000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>7251000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>2997000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>2371000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>2355000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>999000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>3748000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>4494000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>4487000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>6477000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>3743000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>4491000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>4491000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>2499000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>4998000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>9797000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>3498000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>3838000</v>
       </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>16099000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>14849000</v>
+      </c>
+      <c r="F59" s="3">
         <v>18265000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>15845000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>17194000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>16558000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>18865000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>15376000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>15921000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>15273000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>18006000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>15772000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>14119000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>15713000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>17261000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>14445000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>13461000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>12849000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>15574000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>15169000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>13680000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>13372000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>15217000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>14192000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>12852000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>13059000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>14641000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>13556000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>12896000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>13251000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>15292000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>14104000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>12874000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>12441000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>14635000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>13782000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>11811000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>11894000</v>
       </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>40737000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>37795000</v>
+      </c>
+      <c r="F60" s="3">
         <v>39874000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>32643000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>29623000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>29052000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>32045000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>31544000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>24885000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>24407000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>25357000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>23090000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>22880000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>27106000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>34819000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>19511000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>20833000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>18881000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>23071000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>24164000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>20250000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>21347000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>18748000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>17200000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>15740000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>14592000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>18875000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>18630000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>17986000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>20315000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>19562000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>19124000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>17968000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>15494000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>20226000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>24178000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>15790000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>16347000</v>
       </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>148941000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>120871000</v>
+      </c>
+      <c r="F61" s="3">
         <v>100010000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>99510000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>101009000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>91382000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>84991000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>82519000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>82470000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>82468000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>84442000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>86420000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>86396000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>81173000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>75480000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>72110000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>72165000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>73433000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>75970000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>75995000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>63541000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>63531000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>67769000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>69209000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>49299000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>50643000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>50684000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>51656000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>51672000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>51561000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>54386000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>56128000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>55145000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>57119000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>47355000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>47132000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>49518000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>51427000</v>
       </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>15210000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>14626000</v>
+      </c>
+      <c r="F62" s="3">
         <v>14635000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>13893000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>9928000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>9553000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>11038000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>16441000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>17797000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>16576000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>17595000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>16578000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>16652000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>23966000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>25459000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>23444000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>23857000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>24241000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>25013000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>24996000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>24681000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>16520000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>16889000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>16312000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>16784000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>17023000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>17651000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>16060000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>15542000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>15387000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>15846000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>15726000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>16816000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>9849000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>9650000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>9435000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>9051000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>6981000</v>
       </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6391,8 +6687,14 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6504,8 +6806,14 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6617,121 +6925,133 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>206189000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>174527000</v>
+      </c>
+      <c r="F66" s="3">
         <v>155783000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>147392000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>144117000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>134247000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>132945000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>131737000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>130900000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>129946000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>133821000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>132828000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>133532000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>132715000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>136184000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>115517000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>117340000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>116998000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>124465000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>125869000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>109209000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>102097000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>104055000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>103364000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>82469000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>82880000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>87796000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>86924000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>85724000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>87746000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>90291000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>91479000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>90412000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>82894000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>77638000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>81131000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>74767000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>75138000</v>
       </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6771,8 +7091,10 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6884,8 +7206,14 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6997,13 +7325,19 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>4954000</v>
       </c>
       <c r="E70" s="3">
         <v>0</v>
@@ -7110,8 +7444,14 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7223,121 +7563,133 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-7092000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-9355000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-14054000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-15481000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-17368000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-19045000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-20939000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-22628000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-24533000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-25431000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-26428000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-27620000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-29721000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-30617000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-31134000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-31336000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-33147000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-34076000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-25679000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-20120000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-16206000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-17095000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-15410000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-12696000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-10771000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-9174000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-6446000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-3496000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-1284000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>5107000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>12022000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>19111000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>20037000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>28296000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>28586000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>27598000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>25576000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>24375000</v>
       </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7449,8 +7801,14 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7562,8 +7920,14 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7675,121 +8039,133 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>33541000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>29951000</v>
+      </c>
+      <c r="F76" s="3">
         <v>24154000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>20451000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>16730000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>13746000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>10816000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>8704000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>5623000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>3866000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>2370000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1073000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-2421000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-4246000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-5875000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-6220000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-8696000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>-10101000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>-1541000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>5238000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>8900000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>7917000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>9491000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>12074000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>14235000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>15563000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>18433000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>21785000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>23714000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>30572000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>38067000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>46372000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>47789000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>55868000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>55959000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>53860000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>50615000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>48462000</v>
       </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7901,239 +8277,257 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45991</v>
+      </c>
+      <c r="F80" s="2">
         <v>45900</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45808</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45716</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45626</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45535</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45443</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45351</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45260</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45169</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45077</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44985</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44895</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44804</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44712</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44620</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44530</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44439</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44347</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44255</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44165</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44074</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43982</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43890</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43799</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43708</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43616</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43524</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43434</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43343</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43251</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43159</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43069</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42978</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42886</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42794</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42704</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3721000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>6135000</v>
+      </c>
+      <c r="F81" s="3">
         <v>2927000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>3427000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>2936000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>3151000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>2929000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>3144000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>2401000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>2503000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>2420000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>3319000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>1896000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>1741000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>1548000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>3189000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>2319000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-1247000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>2457000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>4032000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>5021000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>2442000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>2251000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>3116000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>2571000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>2311000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>2137000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>3740000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>2745000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>2333000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>2265000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>3276000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-4047000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>2214000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>2144000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>3232000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>2239000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>2032000</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8173,121 +8567,129 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1003000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>908000</v>
+      </c>
+      <c r="F83" s="3">
         <v>804000</v>
       </c>
-      <c r="E83" s="3">
-        <v>811000</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
+        <v>-108000</v>
+      </c>
+      <c r="H83" s="3">
         <v>808000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>798000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>712000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>716000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>672000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>591000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>547000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>563000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>496000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>1498000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>1466000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>831000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>775000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>759000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>757000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>752000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>732000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>731000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>701000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>722000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>748000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>748000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>750000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>754000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>741000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>704000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>720000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>702000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>699000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>688000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>696000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>719000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>656000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>543000</v>
       </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8399,8 +8801,14 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8512,8 +8920,14 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8625,8 +9039,14 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8738,8 +9158,14 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8851,121 +9277,133 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7151000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>2066000</v>
+      </c>
+      <c r="F89" s="3">
         <v>8140000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>6157000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>5933000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>1304000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>7427000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>6081000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>5475000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>143000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>6974000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>5647000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>4275000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>849000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>6394000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>3985000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>3845000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-3682000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>5391000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>4842000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>3704000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>1388000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>5953000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>3614000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>3012000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>513000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>6000000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>4422000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>2861000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>546000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>6722000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>4660000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>3310000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>850000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>6566000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>4466000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>2699000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>1086000</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9005,121 +9443,129 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-18635000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-12033000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-8502000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-9080000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-5862000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-3970000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-2303000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-2798000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1674000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1080000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1314000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1913000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-2628000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-2435000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1719000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-1423000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-1101000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-925000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-1062000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-717000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-414000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-568000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-436000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-433000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-396000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-349000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-386000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-413000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-443000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-421000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-383000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-378000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-286000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-599000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-473000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-525000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-440000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-757000</v>
       </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9231,8 +9677,14 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9344,121 +9796,133 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-19544000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-7714000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-8718000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-9182000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-5976000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-3788000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-2765000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-2766000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1783000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-1249000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-1562000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1612000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-2778000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-2658000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-29436000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-1161000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>2432000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>10730000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-781000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-3911000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-3384000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>3852000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-9655000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-4256000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>480000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>1233000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>12386000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>7906000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>13199000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>1920000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>3532000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>3160000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-1257000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-5710000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-1818000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-5846000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-728000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-9717000</v>
       </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9498,121 +9962,129 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1437000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>1435000</v>
+      </c>
+      <c r="F96" s="3">
         <v>1413000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>1403000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>1119000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>1118000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>1103000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>1102000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>1099000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>1099000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>1091000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>1082000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>863000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-863000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-860000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-854000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-855000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-861000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-887000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-917000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-699000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-717000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-730000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-740000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-768000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-767000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-795000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-806000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-670000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-714000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-742000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AI96" s="3">
         <v>-778000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AJ96" s="3">
         <v>-783000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AK96" s="3">
         <v>-791000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AL96" s="3">
         <v>-788000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AM96" s="3">
         <v>-787000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AN96" s="3">
         <v>-612000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AO96" s="3">
         <v>-614000</v>
       </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9724,8 +10196,14 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9837,8 +10315,14 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9950,343 +10434,367 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>31498000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>14487000</v>
+      </c>
+      <c r="F100" s="3">
         <v>210000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-3814000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>6559000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>2938000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-4585000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-2274000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-2463000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-2289000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-3528000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-2440000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-105000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-1855000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>12310000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-4026000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-1579000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-12053000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-11468000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>6798000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-6129000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-4554000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-6493000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>14133000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-4169000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-8294000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-7802000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-6461000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-12239000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-10023000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-13333000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-5459000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-4020000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>4938000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-5441000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>3287000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-940000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-973000</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-51000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-129000</v>
+      </c>
+      <c r="F101" s="3">
         <v>85000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-68000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>8000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>26000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-36000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-49000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>14000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>29000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-203000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-97000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>46000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>29000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-203000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-97000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>46000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-116000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-181000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>48000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>129000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>39000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>232000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-81000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-34000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>5000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-15000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-73000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>75000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-74000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>-86000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>-228000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>144000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-89000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>230000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>129000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>125000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>-418000</v>
       </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>19214000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>8796000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-341000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-6620000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>6465000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>325000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>162000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>973000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>1237000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-3369000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1848000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>1546000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>1406000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-3635000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-10935000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1299000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>4744000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-5121000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-7039000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>7777000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-5680000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>725000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-9963000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>13410000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-711000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-6543000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>10569000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>5794000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>3896000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-7631000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-3165000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>2133000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-1823000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-11000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>-463000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>2036000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>1156000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>-10022000</v>
       </c>
     </row>
